--- a/Itens.xlsx
+++ b/Itens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC96910-96B4-46E9-A29D-E82095C0A26D}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E249737E-6852-442B-8B54-D1B525E261C6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C00A66D1-236F-4715-AEA0-6613483053F3}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11628" uniqueCount="2358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11766" uniqueCount="2359">
   <si>
     <t>RC</t>
   </si>
@@ -7094,6 +7094,9 @@
   </si>
   <si>
     <t>Coordenador</t>
+  </si>
+  <si>
+    <t>BATCH</t>
   </si>
 </sst>
 </file>
@@ -7650,8 +7653,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CAB39FF7-E7A6-42E7-A4A2-C353F3D3F94B}" name="TabelaItens" displayName="TabelaItens" ref="A1:H3011" totalsRowShown="0">
-  <autoFilter ref="A1:H3011" xr:uid="{CAB39FF7-E7A6-42E7-A4A2-C353F3D3F94B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CAB39FF7-E7A6-42E7-A4A2-C353F3D3F94B}" name="TabelaItens" displayName="TabelaItens" ref="A1:H3057" totalsRowShown="0">
+  <autoFilter ref="A1:H3057" xr:uid="{CAB39FF7-E7A6-42E7-A4A2-C353F3D3F94B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5875FA85-B9CE-4386-BF8C-1C43FF931295}" name="RC"/>
     <tableColumn id="2" xr3:uid="{5C63910C-9FEE-4E72-A34F-1965EEA0ED90}" name="Pedido"/>
@@ -7983,7 +7986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10AC00E0-E0CB-4143-8DA6-F852BC942A11}">
-  <dimension ref="A1:H3011"/>
+  <dimension ref="A1:H3057"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
@@ -78167,6 +78170,1064 @@
         <v>2020</v>
       </c>
     </row>
+    <row r="3012" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3012">
+        <v>1019</v>
+      </c>
+      <c r="B3012">
+        <v>50695</v>
+      </c>
+      <c r="C3012" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3012" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3012">
+        <v>0</v>
+      </c>
+      <c r="F3012" s="1">
+        <v>3805.3</v>
+      </c>
+      <c r="H3012" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="3013" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3013">
+        <v>1019</v>
+      </c>
+      <c r="B3013">
+        <v>50737</v>
+      </c>
+      <c r="C3013" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3013" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3013">
+        <v>0</v>
+      </c>
+      <c r="F3013" s="1">
+        <v>2674.28</v>
+      </c>
+      <c r="H3013" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="3014" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3014">
+        <v>1021</v>
+      </c>
+      <c r="B3014">
+        <v>855376</v>
+      </c>
+      <c r="C3014" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3014" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3014">
+        <v>0</v>
+      </c>
+      <c r="F3014" s="1">
+        <v>4041.37</v>
+      </c>
+      <c r="H3014" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="3015" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3015">
+        <v>134</v>
+      </c>
+      <c r="B3015">
+        <v>855348</v>
+      </c>
+      <c r="C3015" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3015" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3015">
+        <v>0</v>
+      </c>
+      <c r="F3015" s="1">
+        <v>6939.63</v>
+      </c>
+      <c r="H3015" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="3016" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3016">
+        <v>2041</v>
+      </c>
+      <c r="B3016">
+        <v>50733</v>
+      </c>
+      <c r="C3016" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3016" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3016">
+        <v>0</v>
+      </c>
+      <c r="F3016" s="1">
+        <v>2786.27</v>
+      </c>
+      <c r="H3016" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="3017" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3017">
+        <v>2072</v>
+      </c>
+      <c r="B3017">
+        <v>855293</v>
+      </c>
+      <c r="C3017" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3017" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3017">
+        <v>0</v>
+      </c>
+      <c r="F3017" s="1">
+        <v>3427.47</v>
+      </c>
+      <c r="H3017" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="3018" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3018">
+        <v>2083</v>
+      </c>
+      <c r="B3018">
+        <v>855268</v>
+      </c>
+      <c r="C3018" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3018" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3018">
+        <v>0</v>
+      </c>
+      <c r="F3018" s="1">
+        <v>8121.89</v>
+      </c>
+      <c r="H3018" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="3019" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3019">
+        <v>2091</v>
+      </c>
+      <c r="B3019">
+        <v>854960</v>
+      </c>
+      <c r="C3019" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3019" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3019">
+        <v>0</v>
+      </c>
+      <c r="F3019" s="1">
+        <v>8817.06</v>
+      </c>
+      <c r="H3019" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="3020" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3020">
+        <v>2778</v>
+      </c>
+      <c r="B3020">
+        <v>855356</v>
+      </c>
+      <c r="C3020" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3020" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3020">
+        <v>0</v>
+      </c>
+      <c r="F3020" s="1">
+        <v>3420.27</v>
+      </c>
+      <c r="H3020" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="3021" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3021">
+        <v>293</v>
+      </c>
+      <c r="B3021">
+        <v>855374</v>
+      </c>
+      <c r="C3021" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3021" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3021">
+        <v>0</v>
+      </c>
+      <c r="F3021" s="1">
+        <v>5317.8</v>
+      </c>
+      <c r="H3021" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3022">
+        <v>3029</v>
+      </c>
+      <c r="B3022">
+        <v>855341</v>
+      </c>
+      <c r="C3022" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3022" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3022">
+        <v>0</v>
+      </c>
+      <c r="F3022" s="1">
+        <v>700.21</v>
+      </c>
+      <c r="H3022" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="3023" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3023">
+        <v>3034</v>
+      </c>
+      <c r="B3023">
+        <v>855243</v>
+      </c>
+      <c r="C3023" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3023" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3023">
+        <v>0</v>
+      </c>
+      <c r="F3023" s="1">
+        <v>7048.2</v>
+      </c>
+      <c r="H3023" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="3024" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3024">
+        <v>3034</v>
+      </c>
+      <c r="B3024">
+        <v>855315</v>
+      </c>
+      <c r="C3024" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3024" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3024">
+        <v>0</v>
+      </c>
+      <c r="F3024" s="1">
+        <v>12617.36</v>
+      </c>
+      <c r="H3024" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="3025" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3025">
+        <v>3037</v>
+      </c>
+      <c r="B3025">
+        <v>855343</v>
+      </c>
+      <c r="C3025" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3025" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3025">
+        <v>0</v>
+      </c>
+      <c r="F3025" s="1">
+        <v>3913.84</v>
+      </c>
+      <c r="H3025" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="3026" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3026">
+        <v>3060</v>
+      </c>
+      <c r="B3026">
+        <v>855237</v>
+      </c>
+      <c r="C3026" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3026" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3026">
+        <v>0</v>
+      </c>
+      <c r="F3026" s="1">
+        <v>3977.3</v>
+      </c>
+      <c r="H3026" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="3027" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3027">
+        <v>3060</v>
+      </c>
+      <c r="B3027">
+        <v>855248</v>
+      </c>
+      <c r="C3027" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3027" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3027">
+        <v>0</v>
+      </c>
+      <c r="F3027" s="1">
+        <v>3990.57</v>
+      </c>
+      <c r="H3027" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="3028" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3028">
+        <v>3060</v>
+      </c>
+      <c r="B3028">
+        <v>855352</v>
+      </c>
+      <c r="C3028" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3028" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3028">
+        <v>0</v>
+      </c>
+      <c r="F3028" s="1">
+        <v>3382.14</v>
+      </c>
+      <c r="H3028" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="3029" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3029">
+        <v>3064</v>
+      </c>
+      <c r="B3029">
+        <v>854502</v>
+      </c>
+      <c r="C3029" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3029" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3029">
+        <v>0</v>
+      </c>
+      <c r="F3029" s="1">
+        <v>4458.6000000000004</v>
+      </c>
+      <c r="H3029" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="3030" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3030">
+        <v>3069</v>
+      </c>
+      <c r="B3030">
+        <v>854225</v>
+      </c>
+      <c r="C3030" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3030" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3030">
+        <v>0</v>
+      </c>
+      <c r="F3030" s="1">
+        <v>5769.25</v>
+      </c>
+      <c r="H3030" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="3031" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3031">
+        <v>377</v>
+      </c>
+      <c r="B3031">
+        <v>855295</v>
+      </c>
+      <c r="C3031" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3031" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3031">
+        <v>0</v>
+      </c>
+      <c r="F3031" s="1">
+        <v>6437.39</v>
+      </c>
+      <c r="H3031" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="3032" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3032">
+        <v>377</v>
+      </c>
+      <c r="B3032">
+        <v>855351</v>
+      </c>
+      <c r="C3032" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3032" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3032">
+        <v>0</v>
+      </c>
+      <c r="F3032" s="1">
+        <v>4596.7</v>
+      </c>
+      <c r="H3032" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="3033" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3033">
+        <v>380</v>
+      </c>
+      <c r="B3033">
+        <v>855249</v>
+      </c>
+      <c r="C3033" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3033" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3033">
+        <v>0</v>
+      </c>
+      <c r="F3033" s="1">
+        <v>3773.16</v>
+      </c>
+      <c r="H3033" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="3034" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3034">
+        <v>380</v>
+      </c>
+      <c r="B3034">
+        <v>855391</v>
+      </c>
+      <c r="C3034" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3034" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3034">
+        <v>0</v>
+      </c>
+      <c r="F3034" s="1">
+        <v>3141.96</v>
+      </c>
+      <c r="H3034" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="3035" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3035">
+        <v>60</v>
+      </c>
+      <c r="B3035">
+        <v>855291</v>
+      </c>
+      <c r="C3035" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3035" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3035">
+        <v>0</v>
+      </c>
+      <c r="F3035" s="1">
+        <v>5432.47</v>
+      </c>
+      <c r="H3035" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="3036" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3036">
+        <v>614</v>
+      </c>
+      <c r="B3036">
+        <v>855338</v>
+      </c>
+      <c r="C3036" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3036" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3036">
+        <v>0</v>
+      </c>
+      <c r="F3036" s="1">
+        <v>22025.43</v>
+      </c>
+      <c r="H3036" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="3037" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3037">
+        <v>614</v>
+      </c>
+      <c r="B3037">
+        <v>855364</v>
+      </c>
+      <c r="C3037" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3037" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3037">
+        <v>0</v>
+      </c>
+      <c r="F3037" s="1">
+        <v>6411.19</v>
+      </c>
+      <c r="H3037" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="3038" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3038">
+        <v>622</v>
+      </c>
+      <c r="B3038">
+        <v>50741</v>
+      </c>
+      <c r="C3038" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3038" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3038">
+        <v>0</v>
+      </c>
+      <c r="F3038" s="1">
+        <v>2671.23</v>
+      </c>
+      <c r="H3038" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="3039" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3039">
+        <v>639</v>
+      </c>
+      <c r="B3039">
+        <v>855228</v>
+      </c>
+      <c r="C3039" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3039" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3039">
+        <v>0</v>
+      </c>
+      <c r="F3039" s="1">
+        <v>6260.62</v>
+      </c>
+      <c r="H3039" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="3040" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3040">
+        <v>665</v>
+      </c>
+      <c r="B3040">
+        <v>50728</v>
+      </c>
+      <c r="C3040" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3040" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3040">
+        <v>0</v>
+      </c>
+      <c r="F3040" s="1">
+        <v>2346.66</v>
+      </c>
+      <c r="H3040" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3041">
+        <v>703</v>
+      </c>
+      <c r="B3041">
+        <v>855273</v>
+      </c>
+      <c r="C3041" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3041" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3041">
+        <v>0</v>
+      </c>
+      <c r="F3041" s="1">
+        <v>862.3</v>
+      </c>
+      <c r="H3041" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="3042" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3042">
+        <v>703</v>
+      </c>
+      <c r="B3042">
+        <v>855330</v>
+      </c>
+      <c r="C3042" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3042" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3042">
+        <v>0</v>
+      </c>
+      <c r="F3042" s="1">
+        <v>3518.31</v>
+      </c>
+      <c r="H3042" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="3043" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3043">
+        <v>703</v>
+      </c>
+      <c r="B3043">
+        <v>855332</v>
+      </c>
+      <c r="C3043" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3043" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3043">
+        <v>0</v>
+      </c>
+      <c r="F3043" s="1">
+        <v>2856.09</v>
+      </c>
+      <c r="H3043" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="3044" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3044">
+        <v>704</v>
+      </c>
+      <c r="B3044">
+        <v>855337</v>
+      </c>
+      <c r="C3044" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3044" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3044">
+        <v>0</v>
+      </c>
+      <c r="F3044" s="1">
+        <v>3879.75</v>
+      </c>
+      <c r="H3044" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="3045" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3045">
+        <v>773</v>
+      </c>
+      <c r="B3045">
+        <v>855175</v>
+      </c>
+      <c r="C3045" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3045" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3045">
+        <v>0</v>
+      </c>
+      <c r="F3045" s="1">
+        <v>4459.1899999999996</v>
+      </c>
+      <c r="H3045" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="3046" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3046">
+        <v>843</v>
+      </c>
+      <c r="B3046">
+        <v>855402</v>
+      </c>
+      <c r="C3046" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3046" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3046">
+        <v>0</v>
+      </c>
+      <c r="F3046" s="1">
+        <v>14736.29</v>
+      </c>
+      <c r="H3046" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="3047" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3047">
+        <v>851</v>
+      </c>
+      <c r="B3047">
+        <v>854830</v>
+      </c>
+      <c r="C3047" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3047" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3047">
+        <v>0</v>
+      </c>
+      <c r="F3047" s="1">
+        <v>45752.67</v>
+      </c>
+      <c r="H3047" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="3048" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3048">
+        <v>851</v>
+      </c>
+      <c r="B3048">
+        <v>854832</v>
+      </c>
+      <c r="C3048" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3048" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3048">
+        <v>0</v>
+      </c>
+      <c r="F3048" s="1">
+        <v>76254.45</v>
+      </c>
+      <c r="H3048" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="3049" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3049">
+        <v>851</v>
+      </c>
+      <c r="B3049">
+        <v>854835</v>
+      </c>
+      <c r="C3049" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3049" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3049">
+        <v>0</v>
+      </c>
+      <c r="F3049" s="1">
+        <v>3676.72</v>
+      </c>
+      <c r="H3049" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="3050" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3050">
+        <v>874</v>
+      </c>
+      <c r="B3050">
+        <v>855001</v>
+      </c>
+      <c r="C3050" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3050" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3050">
+        <v>0</v>
+      </c>
+      <c r="F3050" s="1">
+        <v>3702.09</v>
+      </c>
+      <c r="H3050" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="3051" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3051">
+        <v>90</v>
+      </c>
+      <c r="B3051">
+        <v>855384</v>
+      </c>
+      <c r="C3051" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3051" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3051">
+        <v>0</v>
+      </c>
+      <c r="F3051" s="1">
+        <v>13047.29</v>
+      </c>
+      <c r="H3051" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="3052" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3052">
+        <v>904</v>
+      </c>
+      <c r="B3052">
+        <v>854925</v>
+      </c>
+      <c r="C3052" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3052" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3052">
+        <v>0</v>
+      </c>
+      <c r="F3052" s="1">
+        <v>4305.6899999999996</v>
+      </c>
+      <c r="H3052" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="3053" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3053">
+        <v>904</v>
+      </c>
+      <c r="B3053">
+        <v>855369</v>
+      </c>
+      <c r="C3053" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3053" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3053">
+        <v>0</v>
+      </c>
+      <c r="F3053" s="1">
+        <v>3989.1</v>
+      </c>
+      <c r="H3053" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="3054" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3054">
+        <v>951</v>
+      </c>
+      <c r="B3054">
+        <v>855274</v>
+      </c>
+      <c r="C3054" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3054" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3054">
+        <v>0</v>
+      </c>
+      <c r="F3054" s="1">
+        <v>4015.43</v>
+      </c>
+      <c r="H3054" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="3055" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3055">
+        <v>967</v>
+      </c>
+      <c r="B3055">
+        <v>854347</v>
+      </c>
+      <c r="C3055" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3055" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3055">
+        <v>0</v>
+      </c>
+      <c r="F3055" s="1">
+        <v>2739.83</v>
+      </c>
+      <c r="H3055" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="3056" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3056">
+        <v>979</v>
+      </c>
+      <c r="B3056">
+        <v>855345</v>
+      </c>
+      <c r="C3056" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3056" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3056">
+        <v>0</v>
+      </c>
+      <c r="F3056" s="1">
+        <v>14321.06</v>
+      </c>
+      <c r="H3056" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="3057" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3057">
+        <v>983</v>
+      </c>
+      <c r="B3057">
+        <v>855327</v>
+      </c>
+      <c r="C3057" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D3057" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3057">
+        <v>0</v>
+      </c>
+      <c r="F3057" s="1">
+        <v>3337.35</v>
+      </c>
+      <c r="H3057" t="s">
+        <v>1913</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">

--- a/Itens.xlsx
+++ b/Itens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61F1E80D-4C39-48F6-86A3-620919CAD857}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B64C65A8-25EB-417B-B802-4CA2961F9B18}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C00A66D1-236F-4715-AEA0-6613483053F3}"/>
   </bookViews>
@@ -9042,7 +9042,7 @@
         <v>303</v>
       </c>
       <c r="G52" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H52" t="s">
         <v>1823</v>
@@ -9165,6 +9165,9 @@
       <c r="F57" s="1" t="s">
         <v>308</v>
       </c>
+      <c r="G57" s="2">
+        <v>46156</v>
+      </c>
       <c r="H57" t="s">
         <v>1822</v>
       </c>
@@ -9235,7 +9238,7 @@
         <v>1429</v>
       </c>
       <c r="G60" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H60" t="s">
         <v>1822</v>
@@ -9537,7 +9540,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H73" t="s">
         <v>1823</v>
@@ -9750,7 +9753,7 @@
         <v>318</v>
       </c>
       <c r="G82" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H82" t="s">
         <v>1811</v>
@@ -9868,7 +9871,7 @@
         <v>323</v>
       </c>
       <c r="G87" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H87" t="s">
         <v>1811</v>
@@ -9894,7 +9897,7 @@
         <v>324</v>
       </c>
       <c r="G88" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H88" t="s">
         <v>1811</v>
@@ -10058,7 +10061,7 @@
         <v>828</v>
       </c>
       <c r="G95" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H95" t="s">
         <v>1811</v>
@@ -10914,6 +10917,9 @@
       <c r="F132" s="1" t="s">
         <v>343</v>
       </c>
+      <c r="G132" s="2">
+        <v>46156</v>
+      </c>
       <c r="H132" t="s">
         <v>1846</v>
       </c>
@@ -10938,7 +10944,7 @@
         <v>344</v>
       </c>
       <c r="G133" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H133" t="s">
         <v>1846</v>
@@ -16798,7 +16804,7 @@
         <v>460</v>
       </c>
       <c r="G387" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H387" t="s">
         <v>1880</v>
@@ -16893,7 +16899,7 @@
         <v>1462</v>
       </c>
       <c r="G391" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H391" t="s">
         <v>1879</v>
@@ -16942,7 +16948,7 @@
         <v>770</v>
       </c>
       <c r="G393" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H393" t="s">
         <v>1879</v>
@@ -17175,7 +17181,7 @@
         <v>470</v>
       </c>
       <c r="G403" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H403" t="s">
         <v>1882</v>
@@ -17201,7 +17207,7 @@
         <v>471</v>
       </c>
       <c r="G404" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H404" t="s">
         <v>1882</v>
@@ -17802,7 +17808,7 @@
         <v>1470</v>
       </c>
       <c r="G430" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H430" t="s">
         <v>1889</v>
@@ -18040,6 +18046,9 @@
       <c r="F440" s="1" t="s">
         <v>1475</v>
       </c>
+      <c r="G440" s="2">
+        <v>46156</v>
+      </c>
       <c r="H440" t="s">
         <v>1896</v>
       </c>
@@ -18064,7 +18073,7 @@
         <v>1476</v>
       </c>
       <c r="G441" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H441" t="s">
         <v>1896</v>
@@ -18181,6 +18190,9 @@
       <c r="F446" s="1" t="s">
         <v>1481</v>
       </c>
+      <c r="G446" s="2">
+        <v>46156</v>
+      </c>
       <c r="H446" t="s">
         <v>1896</v>
       </c>
@@ -18205,7 +18217,7 @@
         <v>1482</v>
       </c>
       <c r="G447" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H447" t="s">
         <v>1896</v>
@@ -20072,7 +20084,7 @@
         <v>513</v>
       </c>
       <c r="G527" s="2">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H527" t="s">
         <v>1848</v>
@@ -20189,6 +20201,9 @@
       <c r="F532" s="1" t="s">
         <v>518</v>
       </c>
+      <c r="G532" s="2">
+        <v>46157</v>
+      </c>
       <c r="H532" t="s">
         <v>1848</v>
       </c>
@@ -22827,7 +22842,7 @@
         <v>2263</v>
       </c>
       <c r="G646" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H646" t="s">
         <v>1823</v>
@@ -25165,7 +25180,7 @@
         <v>542</v>
       </c>
       <c r="G747" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H747" t="s">
         <v>1896</v>
@@ -25467,7 +25482,7 @@
         <v>551</v>
       </c>
       <c r="G760" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H760" t="s">
         <v>1880</v>
@@ -25562,7 +25577,7 @@
         <v>554</v>
       </c>
       <c r="G764" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H764" t="s">
         <v>1880</v>
@@ -25818,7 +25833,7 @@
         <v>551</v>
       </c>
       <c r="G775" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H775" t="s">
         <v>1880</v>
@@ -25959,7 +25974,7 @@
         <v>563</v>
       </c>
       <c r="G781" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H781" t="s">
         <v>1880</v>
@@ -25985,7 +26000,7 @@
         <v>564</v>
       </c>
       <c r="G782" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H782" t="s">
         <v>1880</v>
@@ -26149,7 +26164,7 @@
         <v>546</v>
       </c>
       <c r="G789" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H789" t="s">
         <v>1880</v>
@@ -26244,7 +26259,7 @@
         <v>554</v>
       </c>
       <c r="G793" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H793" t="s">
         <v>1880</v>
@@ -26293,7 +26308,7 @@
         <v>572</v>
       </c>
       <c r="G795" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H795" t="s">
         <v>1880</v>
@@ -26483,7 +26498,7 @@
         <v>580</v>
       </c>
       <c r="G803" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H803" t="s">
         <v>1880</v>
@@ -26532,7 +26547,7 @@
         <v>582</v>
       </c>
       <c r="G805" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H805" t="s">
         <v>1880</v>
@@ -26696,7 +26711,7 @@
         <v>580</v>
       </c>
       <c r="G812" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H812" t="s">
         <v>1880</v>
@@ -26745,7 +26760,7 @@
         <v>586</v>
       </c>
       <c r="G814" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H814" t="s">
         <v>1880</v>
@@ -26840,7 +26855,7 @@
         <v>590</v>
       </c>
       <c r="G818" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H818" t="s">
         <v>1880</v>
@@ -26889,7 +26904,7 @@
         <v>592</v>
       </c>
       <c r="G820" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H820" t="s">
         <v>1880</v>
@@ -26984,7 +26999,7 @@
         <v>590</v>
       </c>
       <c r="G824" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H824" t="s">
         <v>1880</v>
@@ -27010,7 +27025,7 @@
         <v>594</v>
       </c>
       <c r="G825" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H825" t="s">
         <v>1880</v>
@@ -27174,7 +27189,7 @@
         <v>546</v>
       </c>
       <c r="G832" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H832" t="s">
         <v>1880</v>
@@ -27200,7 +27215,7 @@
         <v>564</v>
       </c>
       <c r="G833" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H833" t="s">
         <v>1880</v>
@@ -27295,7 +27310,7 @@
         <v>590</v>
       </c>
       <c r="G837" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H837" t="s">
         <v>1880</v>
@@ -27534,7 +27549,7 @@
         <v>608</v>
       </c>
       <c r="G847" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H847" t="s">
         <v>1880</v>
@@ -27605,6 +27620,9 @@
       <c r="F850" s="1" t="s">
         <v>1242</v>
       </c>
+      <c r="G850" s="2">
+        <v>46156</v>
+      </c>
       <c r="H850" t="s">
         <v>2025</v>
       </c>
@@ -27905,7 +27923,7 @@
         <v>2265</v>
       </c>
       <c r="G863" s="2">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H863" t="s">
         <v>2025</v>
@@ -28805,7 +28823,7 @@
         <v>626</v>
       </c>
       <c r="G902" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H902" t="s">
         <v>1896</v>
@@ -29153,7 +29171,7 @@
         <v>539</v>
       </c>
       <c r="G917" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H917" t="s">
         <v>1896</v>
@@ -30134,7 +30152,7 @@
         <v>0</v>
       </c>
       <c r="G959" s="2">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H959" t="s">
         <v>1984</v>
@@ -30160,7 +30178,7 @@
         <v>0</v>
       </c>
       <c r="G960" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H960" t="s">
         <v>1984</v>
@@ -30347,7 +30365,7 @@
         <v>2267</v>
       </c>
       <c r="G968" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H968" t="s">
         <v>2045</v>
@@ -30608,6 +30626,9 @@
       <c r="F979" s="1" t="s">
         <v>1549</v>
       </c>
+      <c r="G979" s="2">
+        <v>46156</v>
+      </c>
       <c r="H979" t="s">
         <v>2025</v>
       </c>
@@ -31620,6 +31641,9 @@
       <c r="F1023" s="1" t="s">
         <v>1562</v>
       </c>
+      <c r="G1023" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1023" t="s">
         <v>1984</v>
       </c>
@@ -31736,7 +31760,7 @@
         <v>1315</v>
       </c>
       <c r="G1028" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1028" t="s">
         <v>1824</v>
@@ -32090,7 +32114,7 @@
         <v>685</v>
       </c>
       <c r="G1043" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1043" t="s">
         <v>1824</v>
@@ -32139,7 +32163,7 @@
         <v>1012</v>
       </c>
       <c r="G1045" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H1045" t="s">
         <v>1824</v>
@@ -32188,7 +32212,7 @@
         <v>2052</v>
       </c>
       <c r="G1047" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1047" t="s">
         <v>1824</v>
@@ -32443,6 +32467,9 @@
       <c r="F1058" s="1" t="s">
         <v>2059</v>
       </c>
+      <c r="G1058" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1058" t="s">
         <v>1824</v>
       </c>
@@ -32467,7 +32494,7 @@
         <v>2060</v>
       </c>
       <c r="G1059" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1059" t="s">
         <v>1824</v>
@@ -32608,7 +32635,7 @@
         <v>0</v>
       </c>
       <c r="G1065" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H1065" t="s">
         <v>1824</v>
@@ -33375,6 +33402,9 @@
       <c r="F1098" s="1" t="s">
         <v>1580</v>
       </c>
+      <c r="G1098" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1098" t="s">
         <v>1835</v>
       </c>
@@ -33445,7 +33475,7 @@
         <v>1582</v>
       </c>
       <c r="G1101" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1101" t="s">
         <v>1835</v>
@@ -34170,7 +34200,7 @@
         <v>713</v>
       </c>
       <c r="G1132" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1132" t="s">
         <v>1811</v>
@@ -34380,7 +34410,7 @@
         <v>722</v>
       </c>
       <c r="G1141" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1141" t="s">
         <v>1811</v>
@@ -34524,7 +34554,7 @@
         <v>788</v>
       </c>
       <c r="G1147" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1147" t="s">
         <v>1811</v>
@@ -34619,7 +34649,7 @@
         <v>1595</v>
       </c>
       <c r="G1151" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H1151" t="s">
         <v>1811</v>
@@ -34670,6 +34700,9 @@
       <c r="F1153" s="1" t="s">
         <v>1247</v>
       </c>
+      <c r="G1153" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1153" t="s">
         <v>1824</v>
       </c>
@@ -34694,7 +34727,7 @@
         <v>2069</v>
       </c>
       <c r="G1154" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1154" t="s">
         <v>1824</v>
@@ -35232,7 +35265,7 @@
         <v>736</v>
       </c>
       <c r="G1177" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1177" t="s">
         <v>1823</v>
@@ -35327,7 +35360,7 @@
         <v>741</v>
       </c>
       <c r="G1181" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1181" t="s">
         <v>1823</v>
@@ -35399,7 +35432,7 @@
         <v>744</v>
       </c>
       <c r="G1184" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1184" t="s">
         <v>1823</v>
@@ -36210,7 +36243,7 @@
         <v>770</v>
       </c>
       <c r="G1219" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1219" t="s">
         <v>1889</v>
@@ -36489,7 +36522,7 @@
         <v>0</v>
       </c>
       <c r="G1231" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H1231" t="s">
         <v>2036</v>
@@ -36722,7 +36755,7 @@
         <v>775</v>
       </c>
       <c r="G1241" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1241" t="s">
         <v>2036</v>
@@ -36794,7 +36827,7 @@
         <v>1603</v>
       </c>
       <c r="G1244" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1244" t="s">
         <v>1896</v>
@@ -37441,7 +37474,7 @@
         <v>0</v>
       </c>
       <c r="G1272" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H1272" t="s">
         <v>1896</v>
@@ -38658,7 +38691,7 @@
         <v>788</v>
       </c>
       <c r="G1324" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1324" t="s">
         <v>2045</v>
@@ -38707,7 +38740,7 @@
         <v>828</v>
       </c>
       <c r="G1326" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H1326" t="s">
         <v>1881</v>
@@ -38755,6 +38788,9 @@
       <c r="F1328" s="1" t="s">
         <v>527</v>
       </c>
+      <c r="G1328" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1328" t="s">
         <v>1881</v>
       </c>
@@ -38848,7 +38884,7 @@
         <v>785</v>
       </c>
       <c r="G1332" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H1332" t="s">
         <v>1881</v>
@@ -38873,6 +38909,9 @@
       <c r="F1333" s="1" t="s">
         <v>1619</v>
       </c>
+      <c r="G1333" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1333" t="s">
         <v>1881</v>
       </c>
@@ -38943,7 +38982,7 @@
         <v>1622</v>
       </c>
       <c r="G1336" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H1336" t="s">
         <v>1881</v>
@@ -39014,6 +39053,9 @@
       <c r="F1339" s="1" t="s">
         <v>527</v>
       </c>
+      <c r="G1339" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1339" t="s">
         <v>1881</v>
       </c>
@@ -39478,7 +39520,7 @@
         <v>2084</v>
       </c>
       <c r="G1359" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H1359" t="s">
         <v>1881</v>
@@ -41186,6 +41228,9 @@
       <c r="F1432" s="1" t="s">
         <v>308</v>
       </c>
+      <c r="G1432" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1432" t="s">
         <v>1880</v>
       </c>
@@ -41210,7 +41255,7 @@
         <v>807</v>
       </c>
       <c r="G1433" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1433" t="s">
         <v>1880</v>
@@ -41466,7 +41511,7 @@
         <v>2101</v>
       </c>
       <c r="G1444" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1444" t="s">
         <v>1880</v>
@@ -42415,7 +42460,7 @@
         <v>1643</v>
       </c>
       <c r="G1485" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1485" t="s">
         <v>1881</v>
@@ -42579,7 +42624,7 @@
         <v>1641</v>
       </c>
       <c r="G1492" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1492" t="s">
         <v>1881</v>
@@ -42674,7 +42719,7 @@
         <v>1643</v>
       </c>
       <c r="G1496" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1496" t="s">
         <v>1881</v>
@@ -42838,7 +42883,7 @@
         <v>2282</v>
       </c>
       <c r="G1503" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1503" t="s">
         <v>1881</v>
@@ -43001,6 +43046,9 @@
       <c r="F1510" s="1" t="s">
         <v>847</v>
       </c>
+      <c r="G1510" s="2">
+        <v>46171</v>
+      </c>
       <c r="H1510" t="s">
         <v>1873</v>
       </c>
@@ -43024,6 +43072,9 @@
       <c r="F1511" s="1" t="s">
         <v>847</v>
       </c>
+      <c r="G1511" s="2">
+        <v>46171</v>
+      </c>
       <c r="H1511" t="s">
         <v>1873</v>
       </c>
@@ -43185,6 +43236,9 @@
       <c r="F1518" s="1" t="s">
         <v>1644</v>
       </c>
+      <c r="G1518" s="2">
+        <v>46171</v>
+      </c>
       <c r="H1518" t="s">
         <v>1873</v>
       </c>
@@ -43208,6 +43262,9 @@
       <c r="F1519" s="1" t="s">
         <v>1645</v>
       </c>
+      <c r="G1519" s="2">
+        <v>46171</v>
+      </c>
       <c r="H1519" t="s">
         <v>1873</v>
       </c>
@@ -43600,7 +43657,7 @@
         <v>856</v>
       </c>
       <c r="G1536" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H1536" t="s">
         <v>2036</v>
@@ -43879,7 +43936,7 @@
         <v>868</v>
       </c>
       <c r="G1548" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1548" t="s">
         <v>1896</v>
@@ -44020,7 +44077,7 @@
         <v>873</v>
       </c>
       <c r="G1554" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1554" t="s">
         <v>1896</v>
@@ -44138,7 +44195,7 @@
         <v>877</v>
       </c>
       <c r="G1559" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1559" t="s">
         <v>1896</v>
@@ -44440,7 +44497,7 @@
         <v>2110</v>
       </c>
       <c r="G1572" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1572" t="s">
         <v>2036</v>
@@ -44721,6 +44778,9 @@
       <c r="F1584" s="1">
         <v>0</v>
       </c>
+      <c r="G1584" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1584" t="s">
         <v>1896</v>
       </c>
@@ -44816,6 +44876,9 @@
       <c r="F1588" s="1" t="s">
         <v>276</v>
       </c>
+      <c r="G1588" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1588" t="s">
         <v>1896</v>
       </c>
@@ -44840,7 +44903,7 @@
         <v>2114</v>
       </c>
       <c r="G1589" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1589" t="s">
         <v>1896</v>
@@ -45191,7 +45254,7 @@
         <v>883</v>
       </c>
       <c r="G1604" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1604" t="s">
         <v>2118</v>
@@ -45309,7 +45372,7 @@
         <v>888</v>
       </c>
       <c r="G1609" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1609" t="s">
         <v>2118</v>
@@ -45335,7 +45398,7 @@
         <v>889</v>
       </c>
       <c r="G1610" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1610" t="s">
         <v>2118</v>
@@ -45361,7 +45424,7 @@
         <v>889</v>
       </c>
       <c r="G1611" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1611" t="s">
         <v>2118</v>
@@ -45410,7 +45473,7 @@
         <v>892</v>
       </c>
       <c r="G1613" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1613" t="s">
         <v>2118</v>
@@ -45574,7 +45637,7 @@
         <v>898</v>
       </c>
       <c r="G1620" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1620" t="s">
         <v>2118</v>
@@ -45600,7 +45663,7 @@
         <v>900</v>
       </c>
       <c r="G1621" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H1621" t="s">
         <v>2118</v>
@@ -45810,7 +45873,7 @@
         <v>909</v>
       </c>
       <c r="G1630" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1630" t="s">
         <v>2118</v>
@@ -45997,7 +46060,7 @@
         <v>913</v>
       </c>
       <c r="G1638" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1638" t="s">
         <v>2118</v>
@@ -46414,7 +46477,7 @@
         <v>913</v>
       </c>
       <c r="G1656" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1656" t="s">
         <v>2118</v>
@@ -48234,7 +48297,7 @@
         <v>1662</v>
       </c>
       <c r="G1735" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1735" t="s">
         <v>2118</v>
@@ -48896,7 +48959,7 @@
         <v>2120</v>
       </c>
       <c r="G1763" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H1763" t="s">
         <v>1881</v>
@@ -49227,7 +49290,7 @@
         <v>2131</v>
       </c>
       <c r="G1777" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H1777" t="s">
         <v>2045</v>
@@ -49253,7 +49316,7 @@
         <v>2132</v>
       </c>
       <c r="G1778" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1778" t="s">
         <v>2045</v>
@@ -49348,7 +49411,7 @@
         <v>0</v>
       </c>
       <c r="G1782" s="2">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H1782" t="s">
         <v>1881</v>
@@ -49511,6 +49574,9 @@
       <c r="F1789" s="1" t="s">
         <v>972</v>
       </c>
+      <c r="G1789" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1789" t="s">
         <v>1881</v>
       </c>
@@ -51168,7 +51234,7 @@
         <v>999</v>
       </c>
       <c r="G1861" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1861" t="s">
         <v>1881</v>
@@ -53448,7 +53514,7 @@
         <v>1029</v>
       </c>
       <c r="G1960" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1960" t="s">
         <v>1811</v>
@@ -53497,7 +53563,7 @@
         <v>1314</v>
       </c>
       <c r="G1962" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1962" t="s">
         <v>1811</v>
@@ -53568,6 +53634,9 @@
       <c r="F1965" s="1" t="s">
         <v>1688</v>
       </c>
+      <c r="G1965" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1965" t="s">
         <v>1811</v>
       </c>
@@ -53592,7 +53661,7 @@
         <v>1689</v>
       </c>
       <c r="G1966" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1966" t="s">
         <v>1811</v>
@@ -53664,7 +53733,7 @@
         <v>314</v>
       </c>
       <c r="G1969" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1969" t="s">
         <v>1824</v>
@@ -53736,7 +53805,7 @@
         <v>1694</v>
       </c>
       <c r="G1972" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1972" t="s">
         <v>1811</v>
@@ -53946,7 +54015,7 @@
         <v>1694</v>
       </c>
       <c r="G1981" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1981" t="s">
         <v>1811</v>
@@ -54040,6 +54109,9 @@
       <c r="F1985" s="1" t="s">
         <v>2182</v>
       </c>
+      <c r="G1985" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1985" t="s">
         <v>1811</v>
       </c>
@@ -54064,7 +54136,7 @@
         <v>2183</v>
       </c>
       <c r="G1986" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1986" t="s">
         <v>1811</v>
@@ -54090,7 +54162,7 @@
         <v>2184</v>
       </c>
       <c r="G1987" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H1987" t="s">
         <v>1811</v>
@@ -54161,6 +54233,9 @@
       <c r="F1990" s="1" t="s">
         <v>2186</v>
       </c>
+      <c r="G1990" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1990" t="s">
         <v>1811</v>
       </c>
@@ -54185,7 +54260,7 @@
         <v>2187</v>
       </c>
       <c r="G1991" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1991" t="s">
         <v>1811</v>
@@ -54257,7 +54332,7 @@
         <v>2189</v>
       </c>
       <c r="G1994" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H1994" t="s">
         <v>1811</v>
@@ -54490,7 +54565,7 @@
         <v>1035</v>
       </c>
       <c r="G2004" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H2004" t="s">
         <v>1811</v>
@@ -54562,7 +54637,7 @@
         <v>788</v>
       </c>
       <c r="G2007" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2007" t="s">
         <v>1881</v>
@@ -54634,7 +54709,7 @@
         <v>1039</v>
       </c>
       <c r="G2010" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2010" t="s">
         <v>1811</v>
@@ -55028,7 +55103,7 @@
         <v>780</v>
       </c>
       <c r="G2027" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H2027" t="s">
         <v>1811</v>
@@ -55076,6 +55151,9 @@
       <c r="F2029" s="1" t="s">
         <v>1269</v>
       </c>
+      <c r="G2029" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2029" t="s">
         <v>1811</v>
       </c>
@@ -55100,7 +55178,7 @@
         <v>1694</v>
       </c>
       <c r="G2030" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2030" t="s">
         <v>1811</v>
@@ -55402,7 +55480,7 @@
         <v>788</v>
       </c>
       <c r="G2043" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2043" t="s">
         <v>1811</v>
@@ -55496,6 +55574,9 @@
       <c r="F2047" s="1" t="s">
         <v>1018</v>
       </c>
+      <c r="G2047" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2047" t="s">
         <v>1824</v>
       </c>
@@ -55520,7 +55601,7 @@
         <v>1041</v>
       </c>
       <c r="G2048" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2048" t="s">
         <v>1824</v>
@@ -55615,7 +55696,7 @@
         <v>1700</v>
       </c>
       <c r="G2052" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H2052" t="s">
         <v>1811</v>
@@ -56355,7 +56436,7 @@
         <v>1049</v>
       </c>
       <c r="G2083" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2083" t="s">
         <v>1835</v>
@@ -57255,7 +57336,7 @@
         <v>1096</v>
       </c>
       <c r="G2122" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2122" t="s">
         <v>1879</v>
@@ -57306,6 +57387,9 @@
       <c r="F2124" s="1" t="s">
         <v>308</v>
       </c>
+      <c r="G2124" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2124" t="s">
         <v>1880</v>
       </c>
@@ -57427,6 +57511,9 @@
       <c r="F2129" s="1" t="s">
         <v>308</v>
       </c>
+      <c r="G2129" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2129" t="s">
         <v>1879</v>
       </c>
@@ -57750,7 +57837,7 @@
         <v>1100</v>
       </c>
       <c r="G2143" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H2143" t="s">
         <v>1879</v>
@@ -57799,7 +57886,7 @@
         <v>1102</v>
       </c>
       <c r="G2145" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2145" t="s">
         <v>1879</v>
@@ -57848,7 +57935,7 @@
         <v>1104</v>
       </c>
       <c r="G2147" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2147" t="s">
         <v>1879</v>
@@ -57966,7 +58053,7 @@
         <v>1109</v>
       </c>
       <c r="G2152" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2152" t="s">
         <v>1879</v>
@@ -58038,7 +58125,7 @@
         <v>1429</v>
       </c>
       <c r="G2155" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H2155" t="s">
         <v>1880</v>
@@ -58155,6 +58242,9 @@
       <c r="F2160" s="1" t="s">
         <v>1715</v>
       </c>
+      <c r="G2160" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2160" t="s">
         <v>1880</v>
       </c>
@@ -59168,7 +59258,7 @@
         <v>1694</v>
       </c>
       <c r="G2204" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2204" t="s">
         <v>1881</v>
@@ -62741,7 +62831,7 @@
         <v>2212</v>
       </c>
       <c r="G2357" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H2357" t="s">
         <v>1835</v>
@@ -62813,7 +62903,7 @@
         <v>2214</v>
       </c>
       <c r="G2360" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2360" t="s">
         <v>1835</v>
@@ -62934,7 +63024,7 @@
         <v>1728</v>
       </c>
       <c r="G2365" s="2">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H2365" t="s">
         <v>1834</v>
@@ -63397,7 +63487,7 @@
         <v>1229</v>
       </c>
       <c r="G2385" s="2">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H2385" t="s">
         <v>1834</v>
@@ -63745,7 +63835,7 @@
         <v>1740</v>
       </c>
       <c r="G2400" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2400" t="s">
         <v>1984</v>
@@ -63817,7 +63907,7 @@
         <v>1742</v>
       </c>
       <c r="G2403" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2403" t="s">
         <v>1984</v>
@@ -64027,7 +64117,7 @@
         <v>1234</v>
       </c>
       <c r="G2412" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H2412" t="s">
         <v>1882</v>
@@ -64516,7 +64606,7 @@
         <v>1243</v>
       </c>
       <c r="G2433" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H2433" t="s">
         <v>1879</v>
@@ -64634,7 +64724,7 @@
         <v>1250</v>
       </c>
       <c r="G2438" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2438" t="s">
         <v>1811</v>
@@ -64729,7 +64819,7 @@
         <v>685</v>
       </c>
       <c r="G2442" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2442" t="s">
         <v>1824</v>
@@ -64778,7 +64868,7 @@
         <v>719</v>
       </c>
       <c r="G2444" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2444" t="s">
         <v>1811</v>
@@ -64918,6 +65008,9 @@
       <c r="F2450" s="1">
         <v>0</v>
       </c>
+      <c r="G2450" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2450" t="s">
         <v>1824</v>
       </c>
@@ -64942,7 +65035,7 @@
         <v>0</v>
       </c>
       <c r="G2451" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2451" t="s">
         <v>1824</v>
@@ -65200,6 +65293,9 @@
       <c r="F2462" s="1" t="s">
         <v>1018</v>
       </c>
+      <c r="G2462" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2462" t="s">
         <v>1824</v>
       </c>
@@ -65224,7 +65320,7 @@
         <v>1751</v>
       </c>
       <c r="G2463" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2463" t="s">
         <v>1824</v>
@@ -65920,7 +66016,7 @@
         <v>1268</v>
       </c>
       <c r="G2493" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2493" t="s">
         <v>1824</v>
@@ -65969,7 +66065,7 @@
         <v>1272</v>
       </c>
       <c r="G2495" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2495" t="s">
         <v>1811</v>
@@ -66409,7 +66505,7 @@
         <v>1289</v>
       </c>
       <c r="G2514" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2514" t="s">
         <v>1811</v>
@@ -67079,7 +67175,7 @@
         <v>1315</v>
       </c>
       <c r="G2543" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2543" t="s">
         <v>1824</v>
@@ -67174,7 +67270,7 @@
         <v>1317</v>
       </c>
       <c r="G2547" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2547" t="s">
         <v>1811</v>
@@ -67337,6 +67433,9 @@
       <c r="F2554" s="1" t="s">
         <v>1267</v>
       </c>
+      <c r="G2554" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2554" t="s">
         <v>1811</v>
       </c>
@@ -67361,7 +67460,7 @@
         <v>314</v>
       </c>
       <c r="G2555" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2555" t="s">
         <v>1811</v>
@@ -67433,7 +67532,7 @@
         <v>1758</v>
       </c>
       <c r="G2558" s="2">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H2558" t="s">
         <v>1824</v>
@@ -67458,6 +67557,9 @@
       <c r="F2559" s="1" t="s">
         <v>1014</v>
       </c>
+      <c r="G2559" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2559" t="s">
         <v>1824</v>
       </c>
@@ -67482,7 +67584,7 @@
         <v>314</v>
       </c>
       <c r="G2560" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2560" t="s">
         <v>1824</v>
@@ -67577,7 +67679,7 @@
         <v>2230</v>
       </c>
       <c r="G2564" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2564" t="s">
         <v>1824</v>
@@ -67602,6 +67704,9 @@
       <c r="F2565" s="1">
         <v>0</v>
       </c>
+      <c r="G2565" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2565" t="s">
         <v>2175</v>
       </c>
@@ -67626,7 +67731,7 @@
         <v>0</v>
       </c>
       <c r="G2566" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2566" t="s">
         <v>2175</v>
@@ -67727,7 +67832,7 @@
         <v>780</v>
       </c>
       <c r="G2570" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H2570" t="s">
         <v>1811</v>
@@ -67822,7 +67927,7 @@
         <v>2232</v>
       </c>
       <c r="G2574" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2574" t="s">
         <v>1811</v>
@@ -68078,7 +68183,7 @@
         <v>0</v>
       </c>
       <c r="G2585" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="H2585" t="s">
         <v>1870</v>
@@ -68127,7 +68232,7 @@
         <v>0</v>
       </c>
       <c r="G2587" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2587" t="s">
         <v>1870</v>
@@ -69490,7 +69595,7 @@
         <v>1341</v>
       </c>
       <c r="G2643" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2643" t="s">
         <v>2118</v>
@@ -69982,7 +70087,7 @@
         <v>1341</v>
       </c>
       <c r="G2664" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2664" t="s">
         <v>2118</v>
@@ -70195,7 +70300,7 @@
         <v>1341</v>
       </c>
       <c r="G2673" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2673" t="s">
         <v>2118</v>
@@ -70963,7 +71068,7 @@
         <v>1345</v>
       </c>
       <c r="G2706" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H2706" t="s">
         <v>2118</v>
@@ -71202,7 +71307,7 @@
         <v>1345</v>
       </c>
       <c r="G2716" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H2716" t="s">
         <v>2118</v>
@@ -73444,6 +73549,9 @@
       <c r="F2813" s="1" t="s">
         <v>1368</v>
       </c>
+      <c r="G2813" s="2">
+        <v>46265</v>
+      </c>
       <c r="H2813" t="s">
         <v>2025</v>
       </c>
@@ -74414,7 +74522,7 @@
         <v>314</v>
       </c>
       <c r="G2855" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2855" t="s">
         <v>1811</v>
@@ -74830,6 +74938,9 @@
       <c r="F2873" s="1" t="s">
         <v>1408</v>
       </c>
+      <c r="G2873" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2873" t="s">
         <v>1811</v>
       </c>
@@ -74854,7 +74965,7 @@
         <v>722</v>
       </c>
       <c r="G2874" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2874" t="s">
         <v>1811</v>
@@ -74925,6 +75036,9 @@
       <c r="F2877" s="1" t="s">
         <v>1247</v>
       </c>
+      <c r="G2877" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2877" t="s">
         <v>1811</v>
       </c>
@@ -74949,7 +75063,7 @@
         <v>1410</v>
       </c>
       <c r="G2878" s="2">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="H2878" t="s">
         <v>1811</v>
@@ -74974,6 +75088,9 @@
       <c r="F2879" s="1">
         <v>0</v>
       </c>
+      <c r="G2879" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2879" t="s">
         <v>1811</v>
       </c>
@@ -74998,7 +75115,7 @@
         <v>0</v>
       </c>
       <c r="G2880" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2880" t="s">
         <v>1811</v>
@@ -75142,7 +75259,7 @@
         <v>722</v>
       </c>
       <c r="G2886" s="2">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H2886" t="s">
         <v>1811</v>
@@ -75283,7 +75400,7 @@
         <v>1643</v>
       </c>
       <c r="G2892" s="2">
-        <v>46165</v>
+        <v>46154</v>
       </c>
       <c r="H2892" t="s">
         <v>1811</v>
@@ -75408,6 +75525,9 @@
       </c>
       <c r="F2897" s="1" t="s">
         <v>1411</v>
+      </c>
+      <c r="G2897" s="2">
+        <v>46156</v>
       </c>
       <c r="H2897" t="s">
         <v>1984</v>

--- a/Itens.xlsx
+++ b/Itens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FA0F0CC-C761-4925-9811-69B0B989687F}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2A102B3-E261-4913-BD8A-1A3595687C28}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C00A66D1-236F-4715-AEA0-6613483053F3}"/>
+    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{C00A66D1-236F-4715-AEA0-6613483053F3}"/>
   </bookViews>
   <sheets>
     <sheet name="itens" sheetId="1" r:id="rId1"/>
@@ -7637,6 +7637,9 @@
       <c r="F13" s="1" t="s">
         <v>257</v>
       </c>
+      <c r="G13" s="2">
+        <v>46193</v>
+      </c>
       <c r="H13" t="s">
         <v>1014</v>
       </c>
@@ -7660,6 +7663,9 @@
       <c r="F14" s="1" t="s">
         <v>255</v>
       </c>
+      <c r="G14" s="2">
+        <v>46197</v>
+      </c>
       <c r="H14" t="s">
         <v>1014</v>
       </c>
@@ -7683,6 +7689,9 @@
       <c r="F15" s="1" t="s">
         <v>257</v>
       </c>
+      <c r="G15" s="2">
+        <v>46197</v>
+      </c>
       <c r="H15" t="s">
         <v>1014</v>
       </c>
@@ -7706,6 +7715,9 @@
       <c r="F16" s="1" t="s">
         <v>255</v>
       </c>
+      <c r="G16" s="2">
+        <v>46197</v>
+      </c>
       <c r="H16" t="s">
         <v>1014</v>
       </c>
@@ -7729,6 +7741,9 @@
       <c r="F17" s="1" t="s">
         <v>257</v>
       </c>
+      <c r="G17" s="2">
+        <v>46197</v>
+      </c>
       <c r="H17" t="s">
         <v>1014</v>
       </c>
@@ -8454,6 +8469,9 @@
       <c r="F48" s="1" t="s">
         <v>1586</v>
       </c>
+      <c r="G48" s="2">
+        <v>46154</v>
+      </c>
       <c r="H48" t="s">
         <v>1013</v>
       </c>
@@ -8477,6 +8495,9 @@
       <c r="F49" s="1" t="s">
         <v>730</v>
       </c>
+      <c r="G49" s="2">
+        <v>46154</v>
+      </c>
       <c r="H49" t="s">
         <v>1013</v>
       </c>
@@ -8500,6 +8521,9 @@
       <c r="F50" s="1" t="s">
         <v>1587</v>
       </c>
+      <c r="G50" s="2">
+        <v>46154</v>
+      </c>
       <c r="H50" t="s">
         <v>1013</v>
       </c>
@@ -8523,6 +8547,9 @@
       <c r="F51" s="1" t="s">
         <v>1070</v>
       </c>
+      <c r="G51" s="2">
+        <v>46154</v>
+      </c>
       <c r="H51" t="s">
         <v>1013</v>
       </c>
@@ -8546,6 +8573,9 @@
       <c r="F52" s="1" t="s">
         <v>1071</v>
       </c>
+      <c r="G52" s="2">
+        <v>46154</v>
+      </c>
       <c r="H52" t="s">
         <v>1013</v>
       </c>
@@ -8569,6 +8599,9 @@
       <c r="F53" s="1" t="s">
         <v>1071</v>
       </c>
+      <c r="G53" s="2">
+        <v>46154</v>
+      </c>
       <c r="H53" t="s">
         <v>1013</v>
       </c>
@@ -8592,6 +8625,9 @@
       <c r="F54" s="1" t="s">
         <v>749</v>
       </c>
+      <c r="G54" s="2">
+        <v>46154</v>
+      </c>
       <c r="H54" t="s">
         <v>1013</v>
       </c>
@@ -8615,6 +8651,9 @@
       <c r="F55" s="1" t="s">
         <v>1588</v>
       </c>
+      <c r="G55" s="2">
+        <v>46154</v>
+      </c>
       <c r="H55" t="s">
         <v>1013</v>
       </c>
@@ -8638,6 +8677,9 @@
       <c r="F56" s="1" t="s">
         <v>1589</v>
       </c>
+      <c r="G56" s="2">
+        <v>46154</v>
+      </c>
       <c r="H56" t="s">
         <v>1013</v>
       </c>
@@ -9581,6 +9623,9 @@
       <c r="F97" s="1" t="s">
         <v>307</v>
       </c>
+      <c r="G97" s="2">
+        <v>46167</v>
+      </c>
       <c r="H97" t="s">
         <v>1032</v>
       </c>
@@ -9742,6 +9787,9 @@
       <c r="F104" s="1" t="s">
         <v>1035</v>
       </c>
+      <c r="G104" s="2">
+        <v>46156</v>
+      </c>
       <c r="H104" t="s">
         <v>1033</v>
       </c>
@@ -9765,6 +9813,9 @@
       <c r="F105" s="1" t="s">
         <v>1036</v>
       </c>
+      <c r="G105" s="2">
+        <v>46156</v>
+      </c>
       <c r="H105" t="s">
         <v>1033</v>
       </c>
@@ -9788,6 +9839,9 @@
       <c r="F106" s="1" t="s">
         <v>1037</v>
       </c>
+      <c r="G106" s="2">
+        <v>46156</v>
+      </c>
       <c r="H106" t="s">
         <v>1033</v>
       </c>
@@ -9811,6 +9865,9 @@
       <c r="F107" s="1" t="s">
         <v>1038</v>
       </c>
+      <c r="G107" s="2">
+        <v>46156</v>
+      </c>
       <c r="H107" t="s">
         <v>1033</v>
       </c>
@@ -9834,6 +9891,9 @@
       <c r="F108" s="1" t="s">
         <v>1039</v>
       </c>
+      <c r="G108" s="2">
+        <v>46156</v>
+      </c>
       <c r="H108" t="s">
         <v>1033</v>
       </c>
@@ -9857,6 +9917,9 @@
       <c r="F109" s="1" t="s">
         <v>1040</v>
       </c>
+      <c r="G109" s="2">
+        <v>46156</v>
+      </c>
       <c r="H109" t="s">
         <v>1033</v>
       </c>
@@ -9880,6 +9943,9 @@
       <c r="F110" s="1" t="s">
         <v>1041</v>
       </c>
+      <c r="G110" s="2">
+        <v>46156</v>
+      </c>
       <c r="H110" t="s">
         <v>1033</v>
       </c>
@@ -9903,6 +9969,9 @@
       <c r="F111" s="1" t="s">
         <v>1042</v>
       </c>
+      <c r="G111" s="2">
+        <v>46156</v>
+      </c>
       <c r="H111" t="s">
         <v>1033</v>
       </c>
@@ -9926,6 +9995,9 @@
       <c r="F112" s="1" t="s">
         <v>332</v>
       </c>
+      <c r="G112" s="2">
+        <v>46156</v>
+      </c>
       <c r="H112" t="s">
         <v>1033</v>
       </c>
@@ -9949,6 +10021,9 @@
       <c r="F113" s="1" t="s">
         <v>332</v>
       </c>
+      <c r="G113" s="2">
+        <v>46156</v>
+      </c>
       <c r="H113" t="s">
         <v>1033</v>
       </c>
@@ -10608,6 +10683,9 @@
       <c r="F141" s="1" t="s">
         <v>330</v>
       </c>
+      <c r="G141" s="2">
+        <v>46160</v>
+      </c>
       <c r="H141" t="s">
         <v>1046</v>
       </c>
@@ -10631,6 +10709,9 @@
       <c r="F142" s="1" t="s">
         <v>331</v>
       </c>
+      <c r="G142" s="2">
+        <v>46183</v>
+      </c>
       <c r="H142" t="s">
         <v>1046</v>
       </c>
@@ -10654,6 +10735,9 @@
       <c r="F143" s="1" t="s">
         <v>829</v>
       </c>
+      <c r="G143" s="2">
+        <v>46181</v>
+      </c>
       <c r="H143" t="s">
         <v>1046</v>
       </c>
@@ -10677,6 +10761,9 @@
       <c r="F144" s="1" t="s">
         <v>1048</v>
       </c>
+      <c r="G144" s="2">
+        <v>46170</v>
+      </c>
       <c r="H144" t="s">
         <v>1046</v>
       </c>
@@ -10700,6 +10787,9 @@
       <c r="F145" s="1" t="s">
         <v>1593</v>
       </c>
+      <c r="G145" s="2">
+        <v>46171</v>
+      </c>
       <c r="H145" t="s">
         <v>1046</v>
       </c>
@@ -11229,6 +11319,9 @@
       <c r="F168" s="1" t="s">
         <v>1052</v>
       </c>
+      <c r="G168" s="2">
+        <v>46160</v>
+      </c>
       <c r="H168" t="s">
         <v>1032</v>
       </c>
@@ -13078,6 +13171,9 @@
       <c r="F248" s="1" t="s">
         <v>1059</v>
       </c>
+      <c r="G248" s="2">
+        <v>46156</v>
+      </c>
       <c r="H248" t="s">
         <v>1032</v>
       </c>
@@ -13101,6 +13197,9 @@
       <c r="F249" s="1" t="s">
         <v>1060</v>
       </c>
+      <c r="G249" s="2">
+        <v>46156</v>
+      </c>
       <c r="H249" t="s">
         <v>1032</v>
       </c>
@@ -13406,6 +13505,9 @@
       <c r="F262" s="1" t="s">
         <v>1625</v>
       </c>
+      <c r="G262" s="2">
+        <v>46155</v>
+      </c>
       <c r="H262" t="s">
         <v>1064</v>
       </c>
@@ -13429,6 +13531,9 @@
       <c r="F263" s="1" t="s">
         <v>1626</v>
       </c>
+      <c r="G263" s="2">
+        <v>46155</v>
+      </c>
       <c r="H263" t="s">
         <v>1064</v>
       </c>
@@ -14430,6 +14535,9 @@
       <c r="F306" s="1" t="s">
         <v>363</v>
       </c>
+      <c r="G306" s="2">
+        <v>46181</v>
+      </c>
       <c r="H306" t="s">
         <v>1030</v>
       </c>
@@ -17841,6 +17949,9 @@
       <c r="F453" s="1" t="s">
         <v>379</v>
       </c>
+      <c r="G453" s="2">
+        <v>46160</v>
+      </c>
       <c r="H453" t="s">
         <v>1032</v>
       </c>
@@ -20383,6 +20494,9 @@
       <c r="F563" s="1" t="s">
         <v>1676</v>
       </c>
+      <c r="G563" s="2">
+        <v>46156</v>
+      </c>
       <c r="H563" t="s">
         <v>1140</v>
       </c>
@@ -20596,6 +20710,9 @@
       <c r="F572" s="1" t="s">
         <v>1682</v>
       </c>
+      <c r="G572" s="2">
+        <v>46155</v>
+      </c>
       <c r="H572" t="s">
         <v>1054</v>
       </c>
@@ -20619,6 +20736,9 @@
       <c r="F573" s="1" t="s">
         <v>1684</v>
       </c>
+      <c r="G573" s="2">
+        <v>46155</v>
+      </c>
       <c r="H573" t="s">
         <v>1054</v>
       </c>
@@ -20642,6 +20762,9 @@
       <c r="F574" s="1" t="s">
         <v>1685</v>
       </c>
+      <c r="G574" s="2">
+        <v>46155</v>
+      </c>
       <c r="H574" t="s">
         <v>1054</v>
       </c>
@@ -20665,6 +20788,9 @@
       <c r="F575" s="1" t="s">
         <v>1682</v>
       </c>
+      <c r="G575" s="2">
+        <v>46155</v>
+      </c>
       <c r="H575" t="s">
         <v>1054</v>
       </c>
@@ -20688,6 +20814,9 @@
       <c r="F576" s="1" t="s">
         <v>1686</v>
       </c>
+      <c r="G576" s="2">
+        <v>46155</v>
+      </c>
       <c r="H576" t="s">
         <v>1054</v>
       </c>
@@ -20711,6 +20840,9 @@
       <c r="F577" s="1" t="s">
         <v>1682</v>
       </c>
+      <c r="G577" s="2">
+        <v>46155</v>
+      </c>
       <c r="H577" t="s">
         <v>1054</v>
       </c>
@@ -20734,6 +20866,9 @@
       <c r="F578" s="1" t="s">
         <v>1684</v>
       </c>
+      <c r="G578" s="2">
+        <v>46155</v>
+      </c>
       <c r="H578" t="s">
         <v>1054</v>
       </c>
@@ -20757,6 +20892,9 @@
       <c r="F579" s="1" t="s">
         <v>1685</v>
       </c>
+      <c r="G579" s="2">
+        <v>46155</v>
+      </c>
       <c r="H579" t="s">
         <v>1054</v>
       </c>
@@ -20780,6 +20918,9 @@
       <c r="F580" s="1" t="s">
         <v>1682</v>
       </c>
+      <c r="G580" s="2">
+        <v>46155</v>
+      </c>
       <c r="H580" t="s">
         <v>1054</v>
       </c>
@@ -20803,6 +20944,9 @@
       <c r="F581" s="1" t="s">
         <v>1683</v>
       </c>
+      <c r="G581" s="2">
+        <v>46155</v>
+      </c>
       <c r="H581" t="s">
         <v>1054</v>
       </c>
@@ -20826,6 +20970,9 @@
       <c r="F582" s="1" t="s">
         <v>1682</v>
       </c>
+      <c r="G582" s="2">
+        <v>46155</v>
+      </c>
       <c r="H582" t="s">
         <v>1054</v>
       </c>
@@ -20849,6 +20996,9 @@
       <c r="F583" s="1" t="s">
         <v>1683</v>
       </c>
+      <c r="G583" s="2">
+        <v>46155</v>
+      </c>
       <c r="H583" t="s">
         <v>1054</v>
       </c>
@@ -20872,6 +21022,9 @@
       <c r="F584" s="1" t="s">
         <v>1682</v>
       </c>
+      <c r="G584" s="2">
+        <v>46155</v>
+      </c>
       <c r="H584" t="s">
         <v>1054</v>
       </c>
@@ -20895,6 +21048,9 @@
       <c r="F585" s="1" t="s">
         <v>1684</v>
       </c>
+      <c r="G585" s="2">
+        <v>46155</v>
+      </c>
       <c r="H585" t="s">
         <v>1054</v>
       </c>
@@ -20918,6 +21074,9 @@
       <c r="F586" s="1" t="s">
         <v>1683</v>
       </c>
+      <c r="G586" s="2">
+        <v>46155</v>
+      </c>
       <c r="H586" t="s">
         <v>1054</v>
       </c>
@@ -20941,6 +21100,9 @@
       <c r="F587" s="1" t="s">
         <v>1682</v>
       </c>
+      <c r="G587" s="2">
+        <v>46155</v>
+      </c>
       <c r="H587" t="s">
         <v>1054</v>
       </c>
@@ -20964,6 +21126,9 @@
       <c r="F588" s="1" t="s">
         <v>1687</v>
       </c>
+      <c r="G588" s="2">
+        <v>46155</v>
+      </c>
       <c r="H588" t="s">
         <v>1054</v>
       </c>
@@ -20987,6 +21152,9 @@
       <c r="F589" s="1" t="s">
         <v>1682</v>
       </c>
+      <c r="G589" s="2">
+        <v>46155</v>
+      </c>
       <c r="H589" t="s">
         <v>1054</v>
       </c>
@@ -21010,6 +21178,9 @@
       <c r="F590" s="1" t="s">
         <v>1688</v>
       </c>
+      <c r="G590" s="2">
+        <v>46155</v>
+      </c>
       <c r="H590" t="s">
         <v>1054</v>
       </c>
@@ -21033,6 +21204,9 @@
       <c r="F591" s="1" t="s">
         <v>1683</v>
       </c>
+      <c r="G591" s="2">
+        <v>46155</v>
+      </c>
       <c r="H591" t="s">
         <v>1054</v>
       </c>
@@ -22068,6 +22242,9 @@
       <c r="F636" s="1" t="s">
         <v>1141</v>
       </c>
+      <c r="G636" s="2">
+        <v>46203</v>
+      </c>
       <c r="H636" t="s">
         <v>1032</v>
       </c>
@@ -22091,6 +22268,9 @@
       <c r="F637" s="1" t="s">
         <v>1142</v>
       </c>
+      <c r="G637" s="2">
+        <v>46203</v>
+      </c>
       <c r="H637" t="s">
         <v>1032</v>
       </c>
@@ -22114,6 +22294,9 @@
       <c r="F638" s="1" t="s">
         <v>1143</v>
       </c>
+      <c r="G638" s="2">
+        <v>46160</v>
+      </c>
       <c r="H638" t="s">
         <v>1032</v>
       </c>
@@ -22137,6 +22320,9 @@
       <c r="F639" s="1" t="s">
         <v>1145</v>
       </c>
+      <c r="G639" s="2">
+        <v>46160</v>
+      </c>
       <c r="H639" t="s">
         <v>1032</v>
       </c>
@@ -22494,6 +22680,9 @@
       <c r="F654" s="1" t="s">
         <v>1704</v>
       </c>
+      <c r="G654" s="2">
+        <v>46181</v>
+      </c>
       <c r="H654" t="s">
         <v>1032</v>
       </c>
@@ -22586,6 +22775,9 @@
       <c r="F658" s="1" t="s">
         <v>1706</v>
       </c>
+      <c r="G658" s="2">
+        <v>46176</v>
+      </c>
       <c r="H658" t="s">
         <v>1058</v>
       </c>
@@ -22747,6 +22939,9 @@
       <c r="F665" s="1" t="s">
         <v>446</v>
       </c>
+      <c r="G665" s="2">
+        <v>46167</v>
+      </c>
       <c r="H665" t="s">
         <v>1050</v>
       </c>
@@ -22770,6 +22965,9 @@
       <c r="F666" s="1" t="s">
         <v>448</v>
       </c>
+      <c r="G666" s="2">
+        <v>46167</v>
+      </c>
       <c r="H666" t="s">
         <v>1050</v>
       </c>
@@ -22839,6 +23037,9 @@
       <c r="F669" s="1" t="s">
         <v>1339</v>
       </c>
+      <c r="G669" s="2">
+        <v>46170</v>
+      </c>
       <c r="H669" t="s">
         <v>1032</v>
       </c>
@@ -22888,6 +23089,9 @@
       <c r="F671" s="1" t="s">
         <v>1341</v>
       </c>
+      <c r="G671" s="2">
+        <v>46167</v>
+      </c>
       <c r="H671" t="s">
         <v>1050</v>
       </c>
@@ -26553,6 +26757,9 @@
       <c r="F828" s="1" t="s">
         <v>1744</v>
       </c>
+      <c r="G828" s="2">
+        <v>46156</v>
+      </c>
       <c r="H828" t="s">
         <v>1021</v>
       </c>
@@ -26576,6 +26783,9 @@
       <c r="F829" s="1" t="s">
         <v>1745</v>
       </c>
+      <c r="G829" s="2">
+        <v>46156</v>
+      </c>
       <c r="H829" t="s">
         <v>1021</v>
       </c>
@@ -33375,6 +33585,9 @@
       <c r="F1122" s="1" t="s">
         <v>1180</v>
       </c>
+      <c r="G1122" s="2">
+        <v>46202</v>
+      </c>
       <c r="H1122" t="s">
         <v>1050</v>
       </c>
@@ -34876,6 +35089,9 @@
       <c r="F1187" s="1" t="s">
         <v>1430</v>
       </c>
+      <c r="G1187" s="2">
+        <v>46163</v>
+      </c>
       <c r="H1187" t="s">
         <v>1032</v>
       </c>
@@ -35595,6 +35811,9 @@
       <c r="F1218" s="1" t="s">
         <v>1864</v>
       </c>
+      <c r="G1218" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1218" t="s">
         <v>1032</v>
       </c>
@@ -35618,6 +35837,9 @@
       <c r="F1219" s="1" t="s">
         <v>1865</v>
       </c>
+      <c r="G1219" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1219" t="s">
         <v>1032</v>
       </c>
@@ -35641,6 +35863,9 @@
       <c r="F1220" s="1" t="s">
         <v>1866</v>
       </c>
+      <c r="G1220" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1220" t="s">
         <v>1032</v>
       </c>
@@ -37893,6 +38118,9 @@
       <c r="F1317" s="1" t="s">
         <v>556</v>
       </c>
+      <c r="G1317" s="2">
+        <v>46160</v>
+      </c>
       <c r="H1317" t="s">
         <v>1050</v>
       </c>
@@ -37916,6 +38144,9 @@
       <c r="F1318" s="1" t="s">
         <v>557</v>
       </c>
+      <c r="G1318" s="2">
+        <v>46199</v>
+      </c>
       <c r="H1318" t="s">
         <v>1050</v>
       </c>
@@ -37939,6 +38170,9 @@
       <c r="F1319" s="1" t="s">
         <v>558</v>
       </c>
+      <c r="G1319" s="2">
+        <v>46231</v>
+      </c>
       <c r="H1319" t="s">
         <v>1050</v>
       </c>
@@ -37962,6 +38196,9 @@
       <c r="F1320" s="1" t="s">
         <v>559</v>
       </c>
+      <c r="G1320" s="2">
+        <v>46171</v>
+      </c>
       <c r="H1320" t="s">
         <v>1050</v>
       </c>
@@ -38037,6 +38274,9 @@
       <c r="F1323" s="1" t="s">
         <v>561</v>
       </c>
+      <c r="G1323" s="2">
+        <v>46171</v>
+      </c>
       <c r="H1323" t="s">
         <v>1050</v>
       </c>
@@ -38060,6 +38300,9 @@
       <c r="F1324" s="1" t="s">
         <v>562</v>
       </c>
+      <c r="G1324" s="2">
+        <v>46183</v>
+      </c>
       <c r="H1324" t="s">
         <v>1050</v>
       </c>
@@ -38106,6 +38349,9 @@
       <c r="F1326" s="1" t="s">
         <v>563</v>
       </c>
+      <c r="G1326" s="2">
+        <v>46171</v>
+      </c>
       <c r="H1326" t="s">
         <v>1050</v>
       </c>
@@ -38152,6 +38398,9 @@
       <c r="F1328" s="1" t="s">
         <v>565</v>
       </c>
+      <c r="G1328" s="2">
+        <v>46183</v>
+      </c>
       <c r="H1328" t="s">
         <v>1014</v>
       </c>
@@ -38227,6 +38476,9 @@
       <c r="F1331" s="1" t="s">
         <v>924</v>
       </c>
+      <c r="G1331" s="2">
+        <v>46174</v>
+      </c>
       <c r="H1331" t="s">
         <v>1050</v>
       </c>
@@ -38250,6 +38502,9 @@
       <c r="F1332" s="1" t="s">
         <v>925</v>
       </c>
+      <c r="G1332" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1332" t="s">
         <v>1050</v>
       </c>
@@ -38273,6 +38528,9 @@
       <c r="F1333" s="1" t="s">
         <v>1437</v>
       </c>
+      <c r="G1333" s="2">
+        <v>46163</v>
+      </c>
       <c r="H1333" t="s">
         <v>1046</v>
       </c>
@@ -38296,6 +38554,9 @@
       <c r="F1334" s="1" t="s">
         <v>1439</v>
       </c>
+      <c r="G1334" s="2">
+        <v>46170</v>
+      </c>
       <c r="H1334" t="s">
         <v>1069</v>
       </c>
@@ -38319,6 +38580,9 @@
       <c r="F1335" s="1" t="s">
         <v>1440</v>
       </c>
+      <c r="G1335" s="2">
+        <v>46163</v>
+      </c>
       <c r="H1335" t="s">
         <v>1046</v>
       </c>
@@ -41518,6 +41782,9 @@
       <c r="F1472" s="1" t="s">
         <v>1941</v>
       </c>
+      <c r="G1472" s="2">
+        <v>46157</v>
+      </c>
       <c r="H1472" t="s">
         <v>1055</v>
       </c>
@@ -41541,6 +41808,9 @@
       <c r="F1473" s="1">
         <v>0</v>
       </c>
+      <c r="G1473" s="2">
+        <v>46175</v>
+      </c>
       <c r="H1473" t="s">
         <v>1055</v>
       </c>
@@ -41564,6 +41834,9 @@
       <c r="F1474" s="1">
         <v>0</v>
       </c>
+      <c r="G1474" s="2">
+        <v>46175</v>
+      </c>
       <c r="H1474" t="s">
         <v>1055</v>
       </c>
@@ -41587,6 +41860,9 @@
       <c r="F1475" s="1">
         <v>0</v>
       </c>
+      <c r="G1475" s="2">
+        <v>46175</v>
+      </c>
       <c r="H1475" t="s">
         <v>1055</v>
       </c>
@@ -41610,6 +41886,9 @@
       <c r="F1476" s="1">
         <v>0</v>
       </c>
+      <c r="G1476" s="2">
+        <v>46175</v>
+      </c>
       <c r="H1476" t="s">
         <v>1055</v>
       </c>
@@ -41725,6 +42004,9 @@
       <c r="F1481" s="1" t="s">
         <v>1943</v>
       </c>
+      <c r="G1481" s="2">
+        <v>46197</v>
+      </c>
       <c r="H1481" t="s">
         <v>1055</v>
       </c>
@@ -51397,6 +51679,9 @@
       <c r="F1895" s="1">
         <v>0</v>
       </c>
+      <c r="G1895" s="2">
+        <v>46154</v>
+      </c>
       <c r="H1895" t="s">
         <v>1119</v>
       </c>
@@ -51420,6 +51705,9 @@
       <c r="F1896" s="1">
         <v>0</v>
       </c>
+      <c r="G1896" s="2">
+        <v>46154</v>
+      </c>
       <c r="H1896" t="s">
         <v>1119</v>
       </c>
@@ -51443,6 +51731,9 @@
       <c r="F1897" s="1">
         <v>0</v>
       </c>
+      <c r="G1897" s="2">
+        <v>46154</v>
+      </c>
       <c r="H1897" t="s">
         <v>1119</v>
       </c>
@@ -51466,6 +51757,9 @@
       <c r="F1898" s="1">
         <v>0</v>
       </c>
+      <c r="G1898" s="2">
+        <v>46154</v>
+      </c>
       <c r="H1898" t="s">
         <v>1119</v>
       </c>
@@ -51489,6 +51783,9 @@
       <c r="F1899" s="1">
         <v>0</v>
       </c>
+      <c r="G1899" s="2">
+        <v>46154</v>
+      </c>
       <c r="H1899" t="s">
         <v>1119</v>
       </c>
@@ -51742,6 +52039,9 @@
       <c r="F1910" s="1" t="s">
         <v>2055</v>
       </c>
+      <c r="G1910" s="2">
+        <v>46167</v>
+      </c>
       <c r="H1910" t="s">
         <v>1046</v>
       </c>
@@ -51765,6 +52065,9 @@
       <c r="F1911" s="1" t="s">
         <v>2056</v>
       </c>
+      <c r="G1911" s="2">
+        <v>46156</v>
+      </c>
       <c r="H1911" t="s">
         <v>1046</v>
       </c>
@@ -54237,6 +54540,9 @@
       <c r="F2016" s="1" t="s">
         <v>743</v>
       </c>
+      <c r="G2016" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2016" t="s">
         <v>1013</v>
       </c>
@@ -54260,6 +54566,9 @@
       <c r="F2017" s="1" t="s">
         <v>2068</v>
       </c>
+      <c r="G2017" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2017" t="s">
         <v>1013</v>
       </c>
@@ -54381,6 +54690,9 @@
       <c r="F2022" s="1" t="s">
         <v>970</v>
       </c>
+      <c r="G2022" s="2">
+        <v>46160</v>
+      </c>
       <c r="H2022" t="s">
         <v>1049</v>
       </c>
@@ -54453,6 +54765,9 @@
       <c r="F2025" s="1" t="s">
         <v>1240</v>
       </c>
+      <c r="G2025" s="2">
+        <v>46157</v>
+      </c>
       <c r="H2025" t="s">
         <v>1049</v>
       </c>
@@ -54551,6 +54866,9 @@
       <c r="F2029" s="1" t="s">
         <v>970</v>
       </c>
+      <c r="G2029" s="2">
+        <v>46170</v>
+      </c>
       <c r="H2029" t="s">
         <v>1049</v>
       </c>
@@ -54574,6 +54892,9 @@
       <c r="F2030" s="1" t="s">
         <v>1256</v>
       </c>
+      <c r="G2030" s="2">
+        <v>46162</v>
+      </c>
       <c r="H2030" t="s">
         <v>1049</v>
       </c>
@@ -54669,6 +54990,9 @@
       <c r="F2034" s="1" t="s">
         <v>2069</v>
       </c>
+      <c r="G2034" s="2">
+        <v>46170</v>
+      </c>
       <c r="H2034" t="s">
         <v>1049</v>
       </c>
@@ -60619,6 +60943,9 @@
       <c r="F2288" s="1" t="s">
         <v>794</v>
       </c>
+      <c r="G2288" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2288" t="s">
         <v>1140</v>
       </c>
@@ -60642,6 +60969,9 @@
       <c r="F2289" s="1" t="s">
         <v>795</v>
       </c>
+      <c r="G2289" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2289" t="s">
         <v>1140</v>
       </c>
@@ -60665,6 +60995,9 @@
       <c r="F2290" s="1" t="s">
         <v>265</v>
       </c>
+      <c r="G2290" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2290" t="s">
         <v>1140</v>
       </c>
@@ -60688,6 +61021,9 @@
       <c r="F2291" s="1" t="s">
         <v>796</v>
       </c>
+      <c r="G2291" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2291" t="s">
         <v>1140</v>
       </c>
@@ -60711,6 +61047,9 @@
       <c r="F2292" s="1" t="s">
         <v>797</v>
       </c>
+      <c r="G2292" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2292" t="s">
         <v>1140</v>
       </c>
@@ -60734,6 +61073,9 @@
       <c r="F2293" s="1" t="s">
         <v>797</v>
       </c>
+      <c r="G2293" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2293" t="s">
         <v>1140</v>
       </c>
@@ -60757,6 +61099,9 @@
       <c r="F2294" s="1" t="s">
         <v>798</v>
       </c>
+      <c r="G2294" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2294" t="s">
         <v>1140</v>
       </c>
@@ -61312,6 +61657,9 @@
       <c r="F2318" s="1" t="s">
         <v>2103</v>
       </c>
+      <c r="G2318" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2318" t="s">
         <v>1032</v>
       </c>
@@ -61335,6 +61683,9 @@
       <c r="F2319" s="1" t="s">
         <v>2104</v>
       </c>
+      <c r="G2319" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2319" t="s">
         <v>1032</v>
       </c>
@@ -61358,6 +61709,9 @@
       <c r="F2320" s="1" t="s">
         <v>2105</v>
       </c>
+      <c r="G2320" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2320" t="s">
         <v>1032</v>
       </c>
@@ -61381,6 +61735,9 @@
       <c r="F2321" s="1" t="s">
         <v>2106</v>
       </c>
+      <c r="G2321" s="2">
+        <v>46156</v>
+      </c>
       <c r="H2321" t="s">
         <v>1032</v>
       </c>
@@ -62819,6 +63176,9 @@
       <c r="F2383" s="1" t="s">
         <v>821</v>
       </c>
+      <c r="G2383" s="2">
+        <v>46161</v>
+      </c>
       <c r="H2383" t="s">
         <v>1147</v>
       </c>
@@ -62914,6 +63274,9 @@
       <c r="F2387" s="1" t="s">
         <v>821</v>
       </c>
+      <c r="G2387" s="2">
+        <v>46174</v>
+      </c>
       <c r="H2387" t="s">
         <v>1147</v>
       </c>
@@ -64186,6 +64549,9 @@
       <c r="F2441" s="1" t="s">
         <v>826</v>
       </c>
+      <c r="G2441" s="2">
+        <v>46158</v>
+      </c>
       <c r="H2441" t="s">
         <v>1032</v>
       </c>
@@ -64254,6 +64620,9 @@
       </c>
       <c r="F2444" s="1" t="s">
         <v>2138</v>
+      </c>
+      <c r="G2444" s="2">
+        <v>46156</v>
       </c>
       <c r="H2444" t="s">
         <v>1032</v>

--- a/Itens.xlsx
+++ b/Itens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A2818C2-D56C-47FC-AC2B-5CC181FEEBDC}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B46763F-691D-4DFC-96EE-5C14277B8EF8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C00A66D1-236F-4715-AEA0-6613483053F3}"/>
+    <workbookView xWindow="-28920" yWindow="-11205" windowWidth="29040" windowHeight="15840" xr2:uid="{C00A66D1-236F-4715-AEA0-6613483053F3}"/>
   </bookViews>
   <sheets>
     <sheet name="itens" sheetId="1" r:id="rId1"/>
@@ -10738,9 +10738,6 @@
       <c r="F131" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="G131" s="2">
-        <v>46126</v>
-      </c>
       <c r="H131" t="s">
         <v>960</v>
       </c>
@@ -10911,9 +10908,6 @@
       <c r="F138" s="1">
         <v>0</v>
       </c>
-      <c r="G138" s="2">
-        <v>46155</v>
-      </c>
       <c r="H138" t="s">
         <v>961</v>
       </c>
@@ -10937,9 +10931,6 @@
       <c r="F139" s="1">
         <v>0</v>
       </c>
-      <c r="G139" s="2">
-        <v>46155</v>
-      </c>
       <c r="H139" t="s">
         <v>961</v>
       </c>
@@ -10963,9 +10954,6 @@
       <c r="F140" s="1">
         <v>0</v>
       </c>
-      <c r="G140" s="2">
-        <v>46155</v>
-      </c>
       <c r="H140" t="s">
         <v>961</v>
       </c>
@@ -10989,9 +10977,6 @@
       <c r="F141" s="1">
         <v>0</v>
       </c>
-      <c r="G141" s="2">
-        <v>46155</v>
-      </c>
       <c r="H141" t="s">
         <v>961</v>
       </c>
@@ -11015,9 +11000,6 @@
       <c r="F142" s="1">
         <v>0</v>
       </c>
-      <c r="G142" s="2">
-        <v>46155</v>
-      </c>
       <c r="H142" t="s">
         <v>961</v>
       </c>
@@ -11041,9 +11023,6 @@
       <c r="F143" s="1">
         <v>0</v>
       </c>
-      <c r="G143" s="2">
-        <v>46155</v>
-      </c>
       <c r="H143" t="s">
         <v>961</v>
       </c>
@@ -16483,9 +16462,6 @@
       <c r="F377" s="1">
         <v>0</v>
       </c>
-      <c r="G377" s="2">
-        <v>46155</v>
-      </c>
       <c r="H377" t="s">
         <v>947</v>
       </c>
@@ -16509,9 +16485,6 @@
       <c r="F378" s="1">
         <v>0</v>
       </c>
-      <c r="G378" s="2">
-        <v>46155</v>
-      </c>
       <c r="H378" t="s">
         <v>947</v>
       </c>
@@ -16535,9 +16508,6 @@
       <c r="F379" s="1">
         <v>0</v>
       </c>
-      <c r="G379" s="2">
-        <v>46155</v>
-      </c>
       <c r="H379" t="s">
         <v>947</v>
       </c>
@@ -16561,9 +16531,6 @@
       <c r="F380" s="1">
         <v>0</v>
       </c>
-      <c r="G380" s="2">
-        <v>46155</v>
-      </c>
       <c r="H380" t="s">
         <v>947</v>
       </c>
@@ -16587,9 +16554,6 @@
       <c r="F381" s="1">
         <v>0</v>
       </c>
-      <c r="G381" s="2">
-        <v>46155</v>
-      </c>
       <c r="H381" t="s">
         <v>947</v>
       </c>
@@ -16613,9 +16577,6 @@
       <c r="F382" s="1">
         <v>0</v>
       </c>
-      <c r="G382" s="2">
-        <v>46155</v>
-      </c>
       <c r="H382" t="s">
         <v>947</v>
       </c>
@@ -16639,9 +16600,6 @@
       <c r="F383" s="1">
         <v>0</v>
       </c>
-      <c r="G383" s="2">
-        <v>46155</v>
-      </c>
       <c r="H383" t="s">
         <v>947</v>
       </c>
@@ -16665,9 +16623,6 @@
       <c r="F384" s="1">
         <v>0</v>
       </c>
-      <c r="G384" s="2">
-        <v>46155</v>
-      </c>
       <c r="H384" t="s">
         <v>947</v>
       </c>
@@ -16691,9 +16646,6 @@
       <c r="F385" s="1">
         <v>0</v>
       </c>
-      <c r="G385" s="2">
-        <v>46155</v>
-      </c>
       <c r="H385" t="s">
         <v>947</v>
       </c>
@@ -16717,9 +16669,6 @@
       <c r="F386" s="1">
         <v>0</v>
       </c>
-      <c r="G386" s="2">
-        <v>46155</v>
-      </c>
       <c r="H386" t="s">
         <v>947</v>
       </c>
@@ -16743,9 +16692,6 @@
       <c r="F387" s="1">
         <v>0</v>
       </c>
-      <c r="G387" s="2">
-        <v>46155</v>
-      </c>
       <c r="H387" t="s">
         <v>947</v>
       </c>
@@ -16769,9 +16715,6 @@
       <c r="F388" s="1">
         <v>0</v>
       </c>
-      <c r="G388" s="2">
-        <v>46155</v>
-      </c>
       <c r="H388" t="s">
         <v>947</v>
       </c>
@@ -16795,9 +16738,6 @@
       <c r="F389" s="1">
         <v>0</v>
       </c>
-      <c r="G389" s="2">
-        <v>46155</v>
-      </c>
       <c r="H389" t="s">
         <v>947</v>
       </c>
@@ -16821,9 +16761,6 @@
       <c r="F390" s="1">
         <v>0</v>
       </c>
-      <c r="G390" s="2">
-        <v>46155</v>
-      </c>
       <c r="H390" t="s">
         <v>947</v>
       </c>
@@ -16847,9 +16784,6 @@
       <c r="F391" s="1">
         <v>0</v>
       </c>
-      <c r="G391" s="2">
-        <v>46155</v>
-      </c>
       <c r="H391" t="s">
         <v>947</v>
       </c>
@@ -16873,9 +16807,6 @@
       <c r="F392" s="1">
         <v>0</v>
       </c>
-      <c r="G392" s="2">
-        <v>46155</v>
-      </c>
       <c r="H392" t="s">
         <v>947</v>
       </c>
@@ -16899,9 +16830,6 @@
       <c r="F393" s="1">
         <v>0</v>
       </c>
-      <c r="G393" s="2">
-        <v>46155</v>
-      </c>
       <c r="H393" t="s">
         <v>947</v>
       </c>
@@ -16925,9 +16853,6 @@
       <c r="F394" s="1">
         <v>0</v>
       </c>
-      <c r="G394" s="2">
-        <v>46155</v>
-      </c>
       <c r="H394" t="s">
         <v>947</v>
       </c>
@@ -16951,9 +16876,6 @@
       <c r="F395" s="1">
         <v>0</v>
       </c>
-      <c r="G395" s="2">
-        <v>46155</v>
-      </c>
       <c r="H395" t="s">
         <v>947</v>
       </c>
@@ -16977,9 +16899,6 @@
       <c r="F396" s="1">
         <v>0</v>
       </c>
-      <c r="G396" s="2">
-        <v>46155</v>
-      </c>
       <c r="H396" t="s">
         <v>947</v>
       </c>
@@ -17003,9 +16922,6 @@
       <c r="F397" s="1">
         <v>0</v>
       </c>
-      <c r="G397" s="2">
-        <v>46155</v>
-      </c>
       <c r="H397" t="s">
         <v>947</v>
       </c>
@@ -17029,9 +16945,6 @@
       <c r="F398" s="1">
         <v>0</v>
       </c>
-      <c r="G398" s="2">
-        <v>46155</v>
-      </c>
       <c r="H398" t="s">
         <v>947</v>
       </c>
@@ -17055,9 +16968,6 @@
       <c r="F399" s="1">
         <v>0</v>
       </c>
-      <c r="G399" s="2">
-        <v>46155</v>
-      </c>
       <c r="H399" t="s">
         <v>947</v>
       </c>
@@ -17081,9 +16991,6 @@
       <c r="F400" s="1">
         <v>0</v>
       </c>
-      <c r="G400" s="2">
-        <v>46155</v>
-      </c>
       <c r="H400" t="s">
         <v>947</v>
       </c>
@@ -21654,9 +21561,6 @@
       <c r="F597" s="1" t="s">
         <v>1515</v>
       </c>
-      <c r="G597" s="2">
-        <v>46154</v>
-      </c>
       <c r="H597" t="s">
         <v>1064</v>
       </c>
@@ -24583,9 +24487,6 @@
       <c r="F722" s="1">
         <v>0</v>
       </c>
-      <c r="G722" s="2">
-        <v>46155</v>
-      </c>
       <c r="H722" t="s">
         <v>1043</v>
       </c>
@@ -24609,9 +24510,6 @@
       <c r="F723" s="1">
         <v>0</v>
       </c>
-      <c r="G723" s="2">
-        <v>46155</v>
-      </c>
       <c r="H723" t="s">
         <v>1043</v>
       </c>
@@ -24822,9 +24720,6 @@
       <c r="F732" s="1" t="s">
         <v>1999</v>
       </c>
-      <c r="G732" s="2">
-        <v>46155</v>
-      </c>
       <c r="H732" t="s">
         <v>1076</v>
       </c>
@@ -37185,9 +37080,6 @@
       <c r="F1263" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="G1263" s="2">
-        <v>46154</v>
-      </c>
       <c r="H1263" t="s">
         <v>1101</v>
       </c>
@@ -40894,9 +40786,6 @@
       <c r="F1421" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="G1421" s="2">
-        <v>46155</v>
-      </c>
       <c r="H1421" t="s">
         <v>991</v>
       </c>
@@ -40946,9 +40835,6 @@
       <c r="F1423" s="1" t="s">
         <v>2101</v>
       </c>
-      <c r="G1423" s="2">
-        <v>46155</v>
-      </c>
       <c r="H1423" t="s">
         <v>991</v>
       </c>
@@ -40972,9 +40858,6 @@
       <c r="F1424" s="1" t="s">
         <v>2102</v>
       </c>
-      <c r="G1424" s="2">
-        <v>46155</v>
-      </c>
       <c r="H1424" t="s">
         <v>991</v>
       </c>
@@ -40998,9 +40881,6 @@
       <c r="F1425" s="1" t="s">
         <v>2103</v>
       </c>
-      <c r="G1425" s="2">
-        <v>46155</v>
-      </c>
       <c r="H1425" t="s">
         <v>991</v>
       </c>
@@ -41024,9 +40904,6 @@
       <c r="F1426" s="1" t="s">
         <v>2100</v>
       </c>
-      <c r="G1426" s="2">
-        <v>46155</v>
-      </c>
       <c r="H1426" t="s">
         <v>991</v>
       </c>
@@ -41050,9 +40927,6 @@
       <c r="F1427" s="1" t="s">
         <v>2104</v>
       </c>
-      <c r="G1427" s="2">
-        <v>46155</v>
-      </c>
       <c r="H1427" t="s">
         <v>991</v>
       </c>
@@ -41076,9 +40950,6 @@
       <c r="F1428" s="1" t="s">
         <v>2105</v>
       </c>
-      <c r="G1428" s="2">
-        <v>46155</v>
-      </c>
       <c r="H1428" t="s">
         <v>991</v>
       </c>
@@ -41102,9 +40973,6 @@
       <c r="F1429" s="1" t="s">
         <v>2106</v>
       </c>
-      <c r="G1429" s="2">
-        <v>46155</v>
-      </c>
       <c r="H1429" t="s">
         <v>991</v>
       </c>
@@ -46031,9 +45899,6 @@
       <c r="F1639" s="1" t="s">
         <v>2129</v>
       </c>
-      <c r="G1639" s="2">
-        <v>46154</v>
-      </c>
       <c r="H1639" t="s">
         <v>949</v>
       </c>
@@ -46227,9 +46092,6 @@
       <c r="F1647" s="1" t="s">
         <v>2133</v>
       </c>
-      <c r="G1647" s="2">
-        <v>46154</v>
-      </c>
       <c r="H1647" t="s">
         <v>941</v>
       </c>
@@ -53176,9 +53038,6 @@
       <c r="F1943" s="1">
         <v>0</v>
       </c>
-      <c r="G1943" s="2">
-        <v>46154</v>
-      </c>
       <c r="H1943" t="s">
         <v>957</v>
       </c>
@@ -53427,9 +53286,6 @@
       <c r="F1953" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="G1953" s="2">
-        <v>46154</v>
-      </c>
       <c r="H1953" t="s">
         <v>955</v>
       </c>
@@ -53890,9 +53746,6 @@
       <c r="F1973" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="G1973" s="2">
-        <v>46154</v>
-      </c>
       <c r="H1973" t="s">
         <v>955</v>
       </c>
@@ -54011,9 +53864,6 @@
       <c r="F1978" s="1" t="s">
         <v>2209</v>
       </c>
-      <c r="G1978" s="2">
-        <v>46154</v>
-      </c>
       <c r="H1978" t="s">
         <v>955</v>
       </c>
@@ -56350,9 +56200,6 @@
       <c r="F2078" s="1" t="s">
         <v>2229</v>
       </c>
-      <c r="G2078" s="2">
-        <v>46154</v>
-      </c>
       <c r="H2078" t="s">
         <v>1116</v>
       </c>
@@ -56376,9 +56223,6 @@
       <c r="F2079" s="1" t="s">
         <v>2230</v>
       </c>
-      <c r="G2079" s="2">
-        <v>46154</v>
-      </c>
       <c r="H2079" t="s">
         <v>1116</v>
       </c>
@@ -56402,9 +56246,6 @@
       <c r="F2080" s="1" t="s">
         <v>2231</v>
       </c>
-      <c r="G2080" s="2">
-        <v>46154</v>
-      </c>
       <c r="H2080" t="s">
         <v>1116</v>
       </c>
@@ -56929,9 +56770,6 @@
       <c r="F2102" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="G2102" s="2">
-        <v>46154</v>
-      </c>
       <c r="H2102" t="s">
         <v>949</v>
       </c>
@@ -57007,9 +56845,6 @@
       <c r="F2105" s="1" t="s">
         <v>2236</v>
       </c>
-      <c r="G2105" s="2">
-        <v>46155</v>
-      </c>
       <c r="H2105" t="s">
         <v>949</v>
       </c>
@@ -57033,9 +56868,6 @@
       <c r="F2106" s="1" t="s">
         <v>2237</v>
       </c>
-      <c r="G2106" s="2">
-        <v>46155</v>
-      </c>
       <c r="H2106" t="s">
         <v>949</v>
       </c>
@@ -57816,9 +57648,6 @@
       <c r="F2139" s="1" t="s">
         <v>1853</v>
       </c>
-      <c r="G2139" s="2">
-        <v>46155</v>
-      </c>
       <c r="H2139" t="s">
         <v>948</v>
       </c>
@@ -58356,9 +58185,6 @@
       </c>
       <c r="F2162" s="1" t="s">
         <v>1867</v>
-      </c>
-      <c r="G2162" s="2">
-        <v>46155</v>
       </c>
       <c r="H2162" t="s">
         <v>948</v>

--- a/Itens.xlsx
+++ b/Itens.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{618338DD-E96E-4610-B364-B6F45C135E4E}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F5F9552-F93D-4312-833B-16CFF21D6CDE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C00A66D1-236F-4715-AEA0-6613483053F3}"/>
   </bookViews>
   <sheets>
     <sheet name="itens" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -76100,7 +76113,7 @@
         <v>1006</v>
       </c>
       <c r="D2912" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2912">
         <v>0</v>
@@ -76123,7 +76136,7 @@
         <v>1006</v>
       </c>
       <c r="D2913" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2913">
         <v>0</v>
@@ -76146,7 +76159,7 @@
         <v>1006</v>
       </c>
       <c r="D2914" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2914">
         <v>0</v>
@@ -76169,7 +76182,7 @@
         <v>1006</v>
       </c>
       <c r="D2915" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2915">
         <v>0</v>
@@ -76192,7 +76205,7 @@
         <v>1006</v>
       </c>
       <c r="D2916" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2916">
         <v>0</v>
@@ -76215,7 +76228,7 @@
         <v>1006</v>
       </c>
       <c r="D2917" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2917">
         <v>0</v>
@@ -76238,7 +76251,7 @@
         <v>1006</v>
       </c>
       <c r="D2918" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2918">
         <v>0</v>
@@ -76261,7 +76274,7 @@
         <v>1006</v>
       </c>
       <c r="D2919" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2919">
         <v>0</v>
@@ -76284,7 +76297,7 @@
         <v>1006</v>
       </c>
       <c r="D2920" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2920">
         <v>0</v>
@@ -76307,7 +76320,7 @@
         <v>1006</v>
       </c>
       <c r="D2921" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2921">
         <v>0</v>
@@ -76330,7 +76343,7 @@
         <v>1006</v>
       </c>
       <c r="D2922" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2922">
         <v>0</v>
@@ -76353,7 +76366,7 @@
         <v>1006</v>
       </c>
       <c r="D2923" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2923">
         <v>0</v>
@@ -76376,7 +76389,7 @@
         <v>1006</v>
       </c>
       <c r="D2924" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2924">
         <v>0</v>
@@ -76399,7 +76412,7 @@
         <v>1006</v>
       </c>
       <c r="D2925" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2925">
         <v>0</v>
@@ -76422,7 +76435,7 @@
         <v>1006</v>
       </c>
       <c r="D2926" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2926">
         <v>0</v>
@@ -76445,7 +76458,7 @@
         <v>1006</v>
       </c>
       <c r="D2927" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2927">
         <v>0</v>
@@ -76468,7 +76481,7 @@
         <v>1006</v>
       </c>
       <c r="D2928" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2928">
         <v>0</v>
@@ -76491,7 +76504,7 @@
         <v>1006</v>
       </c>
       <c r="D2929" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2929">
         <v>0</v>
@@ -76514,7 +76527,7 @@
         <v>1006</v>
       </c>
       <c r="D2930" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2930">
         <v>0</v>
@@ -76537,7 +76550,7 @@
         <v>1006</v>
       </c>
       <c r="D2931" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2931">
         <v>0</v>
@@ -76560,7 +76573,7 @@
         <v>1006</v>
       </c>
       <c r="D2932" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2932">
         <v>0</v>
@@ -76583,7 +76596,7 @@
         <v>1006</v>
       </c>
       <c r="D2933" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2933">
         <v>0</v>
@@ -76606,7 +76619,7 @@
         <v>1006</v>
       </c>
       <c r="D2934" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2934">
         <v>0</v>
@@ -76629,7 +76642,7 @@
         <v>1006</v>
       </c>
       <c r="D2935" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2935">
         <v>0</v>
@@ -76652,7 +76665,7 @@
         <v>1006</v>
       </c>
       <c r="D2936" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2936">
         <v>0</v>
@@ -76675,7 +76688,7 @@
         <v>1006</v>
       </c>
       <c r="D2937" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2937">
         <v>0</v>
@@ -76698,7 +76711,7 @@
         <v>1006</v>
       </c>
       <c r="D2938" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2938">
         <v>0</v>
@@ -76721,7 +76734,7 @@
         <v>1006</v>
       </c>
       <c r="D2939" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2939">
         <v>0</v>
@@ -76744,7 +76757,7 @@
         <v>1006</v>
       </c>
       <c r="D2940" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2940">
         <v>0</v>
@@ -76767,7 +76780,7 @@
         <v>1006</v>
       </c>
       <c r="D2941" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2941">
         <v>0</v>
@@ -76790,7 +76803,7 @@
         <v>1006</v>
       </c>
       <c r="D2942" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2942">
         <v>0</v>
@@ -76813,7 +76826,7 @@
         <v>1006</v>
       </c>
       <c r="D2943" t="s">
-        <v>23</v>
+        <v>1006</v>
       </c>
       <c r="E2943">
         <v>0</v>

--- a/Itens.xlsx
+++ b/Itens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adere-my.sharepoint.com/personal/alefe_adere_com/Documents/Área de Trabalho/Atendimento/Portal RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60445F52-B284-477C-B7BE-61E298AB37C1}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="13_ncr:9_{EADF24B6-979E-41F6-9DD6-15768FA9F319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6645E8B1-92B8-4481-B885-F8E70B869A15}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C00A66D1-236F-4715-AEA0-6613483053F3}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11567" uniqueCount="2418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11574" uniqueCount="2419">
   <si>
     <t>RC</t>
   </si>
@@ -7287,6 +7287,9 @@
   </si>
   <si>
     <t>8129.54</t>
+  </si>
+  <si>
+    <t>ISOLANTE</t>
   </si>
 </sst>
 </file>
@@ -7432,7 +7435,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7612,6 +7615,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -7773,10 +7782,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -7822,7 +7832,21 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
@@ -7843,16 +7867,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CAB39FF7-E7A6-42E7-A4A2-C353F3D3F94B}" name="TabelaItens" displayName="TabelaItens" ref="A1:H2943" totalsRowShown="0">
-  <autoFilter ref="A1:H2943" xr:uid="{CAB39FF7-E7A6-42E7-A4A2-C353F3D3F94B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CAB39FF7-E7A6-42E7-A4A2-C353F3D3F94B}" name="TabelaItens" displayName="TabelaItens" ref="A1:H2945" totalsRowShown="0">
+  <autoFilter ref="A1:H2945" xr:uid="{CAB39FF7-E7A6-42E7-A4A2-C353F3D3F94B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5875FA85-B9CE-4386-BF8C-1C43FF931295}" name="RC"/>
     <tableColumn id="2" xr3:uid="{5C63910C-9FEE-4E72-A34F-1965EEA0ED90}" name="Pedido"/>
     <tableColumn id="3" xr3:uid="{AC5CDC6D-06DF-4F02-8E98-79F46F57643F}" name="Produto"/>
     <tableColumn id="4" xr3:uid="{570D18AC-F623-4D99-9E81-A3CE4A3BAC3A}" name="Status Reserva"/>
     <tableColumn id="5" xr3:uid="{DD699E9D-5BBB-4A2D-A0E3-154B5B56EC10}" name="Pedido2"/>
-    <tableColumn id="6" xr3:uid="{5029BAFD-740D-4884-B417-DB92003B05D1}" name="Soma de Valor" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{AC21173A-0C61-4FE0-9BC4-82A3B8274D9D}" name="Previsão Final" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{5029BAFD-740D-4884-B417-DB92003B05D1}" name="Soma de Valor" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{AC21173A-0C61-4FE0-9BC4-82A3B8274D9D}" name="Previsão Final" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{D15EC826-6709-4621-905D-53286C6B9654}" name="Coordenador"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -8176,7 +8200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10AC00E0-E0CB-4143-8DA6-F852BC942A11}">
-  <dimension ref="A1:H2943"/>
+  <dimension ref="A1:H2945"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
@@ -72881,7 +72905,7 @@
       <c r="A2774">
         <v>933</v>
       </c>
-      <c r="B2774">
+      <c r="B2774" s="3">
         <v>856292</v>
       </c>
       <c r="C2774" t="s">
@@ -72904,7 +72928,7 @@
       <c r="A2775">
         <v>933</v>
       </c>
-      <c r="B2775">
+      <c r="B2775" s="3">
         <v>856292</v>
       </c>
       <c r="C2775" t="s">
@@ -72927,7 +72951,7 @@
       <c r="A2776">
         <v>933</v>
       </c>
-      <c r="B2776">
+      <c r="B2776" s="3">
         <v>856292</v>
       </c>
       <c r="C2776" t="s">
@@ -72950,7 +72974,7 @@
       <c r="A2777">
         <v>933</v>
       </c>
-      <c r="B2777">
+      <c r="B2777" s="3">
         <v>856292</v>
       </c>
       <c r="C2777" t="s">
@@ -72973,7 +72997,7 @@
       <c r="A2778">
         <v>933</v>
       </c>
-      <c r="B2778">
+      <c r="B2778" s="3">
         <v>856292</v>
       </c>
       <c r="C2778" t="s">
@@ -76886,7 +76910,7 @@
       <c r="A2942">
         <v>933</v>
       </c>
-      <c r="B2942">
+      <c r="B2942" s="3">
         <v>856292</v>
       </c>
       <c r="C2942" t="s">
@@ -76932,6 +76956,55 @@
       </c>
       <c r="H2943" t="s">
         <v>833</v>
+      </c>
+    </row>
+    <row r="2944" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2944">
+        <v>1</v>
+      </c>
+      <c r="B2944">
+        <v>999999</v>
+      </c>
+      <c r="C2944" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D2944" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E2944">
+        <v>0</v>
+      </c>
+      <c r="F2944" s="1">
+        <v>2791.13</v>
+      </c>
+      <c r="G2944" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H2944" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="2945" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2945">
+        <v>1</v>
+      </c>
+      <c r="B2945">
+        <v>999999</v>
+      </c>
+      <c r="C2945" t="s">
+        <v>2418</v>
+      </c>
+      <c r="D2945" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2945">
+        <v>10</v>
+      </c>
+      <c r="F2945" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2945" t="s">
+        <v>972</v>
       </c>
     </row>
   </sheetData>
